--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2450,6 +2450,230 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125044699</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>380821</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6771374</v>
+      </c>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125049340</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Abelåsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>380860</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6771171</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -8491,10 +8491,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125070190</v>
+        <v>125044277</v>
       </c>
       <c r="B73" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8507,37 +8507,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>381088</v>
+        <v>380886</v>
       </c>
       <c r="R73" t="n">
-        <v>6771369</v>
+        <v>6771400</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8564,36 +8567,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125070214</v>
+        <v>125049404</v>
       </c>
       <c r="B74" t="n">
         <v>78810</v>
@@ -8627,19 +8641,22 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>381359</v>
+        <v>381342</v>
       </c>
       <c r="R74" t="n">
-        <v>6771390</v>
+        <v>6771402</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8666,39 +8683,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125070265</v>
+        <v>125048940</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8711,37 +8739,40 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>380882</v>
+        <v>381311</v>
       </c>
       <c r="R75" t="n">
-        <v>6771534</v>
+        <v>6771438</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8768,39 +8799,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125070266</v>
+        <v>125041905</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8813,37 +8855,40 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>380889</v>
+        <v>380904</v>
       </c>
       <c r="R76" t="n">
-        <v>6771552</v>
+        <v>6771257</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8870,39 +8915,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125070206</v>
+        <v>125045234</v>
       </c>
       <c r="B77" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8915,37 +8971,40 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>380765</v>
+        <v>380888</v>
       </c>
       <c r="R77" t="n">
-        <v>6771036</v>
+        <v>6771588</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8972,39 +9031,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125049925</v>
+        <v>125040078</v>
       </c>
       <c r="B78" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9017,40 +9087,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>381316</v>
+        <v>380836</v>
       </c>
       <c r="R78" t="n">
-        <v>6771194</v>
+        <v>6771174</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9079,7 +9146,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9089,7 +9156,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9098,29 +9165,28 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125045567</v>
+        <v>125070190</v>
       </c>
       <c r="B79" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9133,40 +9199,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>380944</v>
+        <v>381088</v>
       </c>
       <c r="R79" t="n">
-        <v>6771491</v>
+        <v>6771369</v>
       </c>
       <c r="S79" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9193,50 +9256,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125070191</v>
+        <v>125070214</v>
       </c>
       <c r="B80" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9249,21 +9301,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9273,10 +9325,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>380812</v>
+        <v>381359</v>
       </c>
       <c r="R80" t="n">
-        <v>6771477</v>
+        <v>6771390</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9335,7 +9387,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125070237</v>
+        <v>125070265</v>
       </c>
       <c r="B81" t="n">
         <v>78810</v>
@@ -9375,10 +9427,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>380923</v>
+        <v>380882</v>
       </c>
       <c r="R81" t="n">
-        <v>6771536</v>
+        <v>6771534</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9437,7 +9489,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125070269</v>
+        <v>125070266</v>
       </c>
       <c r="B82" t="n">
         <v>78810</v>
@@ -9477,10 +9529,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>380938</v>
+        <v>380889</v>
       </c>
       <c r="R82" t="n">
-        <v>6771234</v>
+        <v>6771552</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9539,10 +9591,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125044277</v>
+        <v>125070206</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9555,40 +9607,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>380886</v>
+        <v>380765</v>
       </c>
       <c r="R83" t="n">
-        <v>6771400</v>
+        <v>6771036</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9615,50 +9664,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125049404</v>
+        <v>125049925</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9671,21 +9709,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9694,14 +9732,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>381342</v>
+        <v>381316</v>
       </c>
       <c r="R84" t="n">
-        <v>6771402</v>
+        <v>6771194</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9733,7 +9771,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9743,7 +9781,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9759,22 +9797,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125048940</v>
+        <v>125045567</v>
       </c>
       <c r="B85" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9787,21 +9825,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9810,17 +9848,17 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>381311</v>
+        <v>380944</v>
       </c>
       <c r="R85" t="n">
-        <v>6771438</v>
+        <v>6771491</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9849,7 +9887,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9859,7 +9897,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9875,22 +9913,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125041905</v>
+        <v>125070191</v>
       </c>
       <c r="B86" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9903,40 +9941,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>380904</v>
+        <v>380812</v>
       </c>
       <c r="R86" t="n">
-        <v>6771257</v>
+        <v>6771477</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9963,47 +9998,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125045234</v>
+        <v>125070237</v>
       </c>
       <c r="B87" t="n">
         <v>78810</v>
@@ -10037,22 +10061,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>380888</v>
+        <v>380923</v>
       </c>
       <c r="R87" t="n">
-        <v>6771588</v>
+        <v>6771536</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10079,47 +10100,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125040078</v>
+        <v>125070269</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -10155,14 +10165,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>380836</v>
+        <v>380938</v>
       </c>
       <c r="R88" t="n">
-        <v>6771174</v>
+        <v>6771234</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -10192,19 +10202,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10219,12 +10219,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -12517,10 +12517,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125049054</v>
+        <v>125070209</v>
       </c>
       <c r="B110" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12533,40 +12533,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>381309</v>
+        <v>381523</v>
       </c>
       <c r="R110" t="n">
-        <v>6771459</v>
+        <v>6771219</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12593,47 +12590,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125044481</v>
+        <v>125070211</v>
       </c>
       <c r="B111" t="n">
         <v>78810</v>
@@ -12667,22 +12653,19 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>380836</v>
+        <v>381359</v>
       </c>
       <c r="R111" t="n">
-        <v>6771422</v>
+        <v>6771263</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12709,50 +12692,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125046270</v>
+        <v>125070239</v>
       </c>
       <c r="B112" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12765,40 +12737,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>381095</v>
+        <v>380922</v>
       </c>
       <c r="R112" t="n">
-        <v>6771385</v>
+        <v>6771536</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12825,47 +12794,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
       <c r="AE112" t="b">
         <v>0</v>
       </c>
-      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125070209</v>
+        <v>125070254</v>
       </c>
       <c r="B113" t="n">
         <v>78810</v>
@@ -12905,10 +12863,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>381523</v>
+        <v>380901</v>
       </c>
       <c r="R113" t="n">
-        <v>6771219</v>
+        <v>6771241</v>
       </c>
       <c r="S113" t="n">
         <v>15</v>
@@ -12967,10 +12925,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125070211</v>
+        <v>125049054</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12983,37 +12941,40 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>381359</v>
+        <v>381309</v>
       </c>
       <c r="R114" t="n">
-        <v>6771263</v>
+        <v>6771459</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13040,36 +13001,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125070239</v>
+        <v>125044481</v>
       </c>
       <c r="B115" t="n">
         <v>78810</v>
@@ -13103,19 +13075,22 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>380922</v>
+        <v>380836</v>
       </c>
       <c r="R115" t="n">
-        <v>6771536</v>
+        <v>6771422</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13142,39 +13117,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125070254</v>
+        <v>125046270</v>
       </c>
       <c r="B116" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13187,37 +13173,40 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>380901</v>
+        <v>381095</v>
       </c>
       <c r="R116" t="n">
-        <v>6771241</v>
+        <v>6771385</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13244,39 +13233,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125050284</v>
+        <v>125070193</v>
       </c>
       <c r="B117" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13289,37 +13289,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>381346</v>
+        <v>380811</v>
       </c>
       <c r="R117" t="n">
-        <v>6771055</v>
+        <v>6771473</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13349,50 +13346,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125042523</v>
+        <v>125070256</v>
       </c>
       <c r="B118" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13405,40 +13391,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>381014</v>
+        <v>380801</v>
       </c>
       <c r="R118" t="n">
-        <v>6771206</v>
+        <v>6771192</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13465,50 +13448,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125050619</v>
+        <v>125070232</v>
       </c>
       <c r="B119" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13521,37 +13493,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>381293</v>
+        <v>380944</v>
       </c>
       <c r="R119" t="n">
-        <v>6770938</v>
+        <v>6771499</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13581,47 +13550,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125045538</v>
+        <v>125070248</v>
       </c>
       <c r="B120" t="n">
         <v>78810</v>
@@ -13655,22 +13613,19 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>380927</v>
+        <v>380858</v>
       </c>
       <c r="R120" t="n">
-        <v>6771538</v>
+        <v>6771400</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13697,47 +13652,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125040285</v>
+        <v>125045155</v>
       </c>
       <c r="B121" t="n">
         <v>78810</v>
@@ -13771,19 +13715,22 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>380823</v>
+        <v>380803</v>
       </c>
       <c r="R121" t="n">
-        <v>6771160</v>
+        <v>6771421</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13812,7 +13759,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13822,7 +13769,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13831,25 +13778,26 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125049508</v>
+        <v>125050284</v>
       </c>
       <c r="B122" t="n">
         <v>78546</v>
@@ -13892,13 +13840,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>381324</v>
+        <v>381346</v>
       </c>
       <c r="R122" t="n">
-        <v>6771331</v>
+        <v>6771055</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13927,7 +13875,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13937,7 +13885,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13965,10 +13913,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125048909</v>
+        <v>125042523</v>
       </c>
       <c r="B123" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13981,21 +13929,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14008,10 +13956,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>381320</v>
+        <v>381014</v>
       </c>
       <c r="R123" t="n">
-        <v>6771437</v>
+        <v>6771206</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14043,7 +13991,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14053,7 +14001,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14074,17 +14022,17 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125070193</v>
+        <v>125050619</v>
       </c>
       <c r="B124" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14097,34 +14045,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>380811</v>
+        <v>381293</v>
       </c>
       <c r="R124" t="n">
-        <v>6771473</v>
+        <v>6770938</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -14154,36 +14105,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125070256</v>
+        <v>125045538</v>
       </c>
       <c r="B125" t="n">
         <v>78810</v>
@@ -14217,19 +14179,22 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>380801</v>
+        <v>380927</v>
       </c>
       <c r="R125" t="n">
-        <v>6771192</v>
+        <v>6771538</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14256,36 +14221,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125070232</v>
+        <v>125040285</v>
       </c>
       <c r="B126" t="n">
         <v>78810</v>
@@ -14321,17 +14297,17 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>380944</v>
+        <v>380823</v>
       </c>
       <c r="R126" t="n">
-        <v>6771499</v>
+        <v>6771160</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14358,9 +14334,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14375,22 +14361,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125070248</v>
+        <v>125049508</v>
       </c>
       <c r="B127" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14403,37 +14389,40 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>380858</v>
+        <v>381324</v>
       </c>
       <c r="R127" t="n">
-        <v>6771400</v>
+        <v>6771331</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14460,36 +14449,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125045155</v>
+        <v>125048909</v>
       </c>
       <c r="B128" t="n">
         <v>78810</v>
@@ -14528,17 +14528,17 @@
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>380803</v>
+        <v>381320</v>
       </c>
       <c r="R128" t="n">
-        <v>6771421</v>
+        <v>6771437</v>
       </c>
       <c r="S128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14593,12 +14593,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -16244,10 +16244,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125070249</v>
+        <v>125041208</v>
       </c>
       <c r="B144" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16260,37 +16260,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>380872</v>
+        <v>380840</v>
       </c>
       <c r="R144" t="n">
-        <v>6771395</v>
+        <v>6771239</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16317,9 +16317,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16334,19 +16344,19 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125070255</v>
+        <v>125070249</v>
       </c>
       <c r="B145" t="n">
         <v>78810</v>
@@ -16386,10 +16396,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>380893</v>
+        <v>380872</v>
       </c>
       <c r="R145" t="n">
-        <v>6771236</v>
+        <v>6771395</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16448,10 +16458,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125039976</v>
+        <v>125070255</v>
       </c>
       <c r="B146" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16464,40 +16474,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>380856</v>
+        <v>380893</v>
       </c>
       <c r="R146" t="n">
-        <v>6771167</v>
+        <v>6771236</v>
       </c>
       <c r="S146" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16524,50 +16531,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125070267</v>
+        <v>125039976</v>
       </c>
       <c r="B147" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16580,37 +16576,40 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>380852</v>
+        <v>380856</v>
       </c>
       <c r="R147" t="n">
-        <v>6771474</v>
+        <v>6771167</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16637,39 +16636,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AD147" t="b">
         <v>0</v>
       </c>
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125041208</v>
+        <v>125070267</v>
       </c>
       <c r="B148" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16682,37 +16692,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>380840</v>
+        <v>380852</v>
       </c>
       <c r="R148" t="n">
-        <v>6771239</v>
+        <v>6771474</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16739,19 +16749,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>12:11</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16766,12 +16766,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -2796,7 +2796,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125070241</v>
+        <v>125044979</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2830,19 +2830,22 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380908</v>
+        <v>380890</v>
       </c>
       <c r="R21" t="n">
-        <v>6771533</v>
+        <v>6771528</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2869,36 +2872,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125070261</v>
+        <v>125039764</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2934,14 +2948,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Vålviken, Vålviken, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>381036</v>
+        <v>380927</v>
       </c>
       <c r="R22" t="n">
-        <v>6771447</v>
+        <v>6771248</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2971,9 +2985,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,7 +3024,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125070256</v>
+        <v>125041252</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3036,17 +3060,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380801</v>
+        <v>380848</v>
       </c>
       <c r="R23" t="n">
-        <v>6771192</v>
+        <v>6771237</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3073,9 +3097,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3090,22 +3124,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125070218</v>
+        <v>125040653</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3118,37 +3152,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>381266</v>
+        <v>380872</v>
       </c>
       <c r="R24" t="n">
-        <v>6771351</v>
+        <v>6771195</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3175,39 +3212,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125070227</v>
+        <v>125040326</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3220,37 +3268,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380995</v>
+        <v>380824</v>
       </c>
       <c r="R25" t="n">
-        <v>6771436</v>
+        <v>6771177</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3277,9 +3325,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3294,22 +3352,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125070238</v>
+        <v>125049457</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3322,34 +3380,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>380917</v>
+        <v>380860</v>
       </c>
       <c r="R26" t="n">
-        <v>6771547</v>
+        <v>6771171</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3379,9 +3437,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3396,19 +3464,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125044979</v>
+        <v>125070241</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3442,22 +3510,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380890</v>
+        <v>380908</v>
       </c>
       <c r="R27" t="n">
-        <v>6771528</v>
+        <v>6771533</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3484,47 +3549,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125039764</v>
+        <v>125070261</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3560,14 +3614,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vålviken, Vålviken, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>380927</v>
+        <v>381036</v>
       </c>
       <c r="R28" t="n">
-        <v>6771248</v>
+        <v>6771447</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3597,19 +3651,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3636,7 +3680,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125041252</v>
+        <v>125070256</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3672,17 +3716,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380848</v>
+        <v>380801</v>
       </c>
       <c r="R29" t="n">
-        <v>6771237</v>
+        <v>6771192</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3709,19 +3753,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3736,22 +3770,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125040653</v>
+        <v>125070218</v>
       </c>
       <c r="B30" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3764,40 +3798,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380872</v>
+        <v>381266</v>
       </c>
       <c r="R30" t="n">
-        <v>6771195</v>
+        <v>6771351</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3824,50 +3855,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125040326</v>
+        <v>125070227</v>
       </c>
       <c r="B31" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3880,37 +3900,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380824</v>
+        <v>380995</v>
       </c>
       <c r="R31" t="n">
-        <v>6771177</v>
+        <v>6771436</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3937,19 +3957,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3964,22 +3974,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125049457</v>
+        <v>125070238</v>
       </c>
       <c r="B32" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3992,34 +4002,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380860</v>
+        <v>380917</v>
       </c>
       <c r="R32" t="n">
-        <v>6771171</v>
+        <v>6771547</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4049,19 +4059,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4076,22 +4076,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125070203</v>
+        <v>125046270</v>
       </c>
       <c r="B33" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4104,37 +4104,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381386</v>
+        <v>381095</v>
       </c>
       <c r="R33" t="n">
-        <v>6771403</v>
+        <v>6771385</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4161,39 +4164,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125070250</v>
+        <v>125049925</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4206,37 +4220,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380990</v>
+        <v>381316</v>
       </c>
       <c r="R34" t="n">
-        <v>6771182</v>
+        <v>6771194</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4263,39 +4280,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125070269</v>
+        <v>125047288</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4308,37 +4336,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380938</v>
+        <v>381041</v>
       </c>
       <c r="R35" t="n">
-        <v>6771234</v>
+        <v>6771405</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4365,29 +4396,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4510,10 +4552,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125046270</v>
+        <v>125070203</v>
       </c>
       <c r="B37" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4526,40 +4568,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>381095</v>
+        <v>381386</v>
       </c>
       <c r="R37" t="n">
-        <v>6771385</v>
+        <v>6771403</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4586,50 +4625,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125049925</v>
+        <v>125070250</v>
       </c>
       <c r="B38" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4642,40 +4670,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>381316</v>
+        <v>380990</v>
       </c>
       <c r="R38" t="n">
-        <v>6771194</v>
+        <v>6771182</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4702,50 +4727,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125047288</v>
+        <v>125070269</v>
       </c>
       <c r="B39" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4758,40 +4772,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>381041</v>
+        <v>380938</v>
       </c>
       <c r="R39" t="n">
-        <v>6771405</v>
+        <v>6771234</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4818,40 +4829,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125070201</v>
+        <v>125041099</v>
       </c>
       <c r="B56" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6606,37 +6606,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>380953</v>
+        <v>380825</v>
       </c>
       <c r="R56" t="n">
-        <v>6771491</v>
+        <v>6771235</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6663,9 +6663,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6680,22 +6690,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125050542</v>
+        <v>125041141</v>
       </c>
       <c r="B57" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6708,37 +6718,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>381332</v>
+        <v>380828</v>
       </c>
       <c r="R57" t="n">
-        <v>6770903</v>
+        <v>6771239</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6770,7 +6777,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6780,7 +6787,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6789,7 +6796,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6801,17 +6807,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125041141</v>
+        <v>125044513</v>
       </c>
       <c r="B58" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6824,24 +6830,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
@@ -6851,7 +6860,7 @@
         <v>380828</v>
       </c>
       <c r="R58" t="n">
-        <v>6771239</v>
+        <v>6771432</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6883,7 +6892,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6893,7 +6902,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6902,6 +6911,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6913,14 +6923,14 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125044513</v>
+        <v>125040302</v>
       </c>
       <c r="B59" t="n">
         <v>78810</v>
@@ -6954,19 +6964,16 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>380828</v>
+        <v>380817</v>
       </c>
       <c r="R59" t="n">
-        <v>6771432</v>
+        <v>6771175</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6998,7 +7005,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7008,7 +7015,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7017,7 +7024,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7029,14 +7035,14 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125040302</v>
+        <v>125041757</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -7076,10 +7082,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>380817</v>
+        <v>380887</v>
       </c>
       <c r="R60" t="n">
-        <v>6771175</v>
+        <v>6771232</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7111,7 +7117,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7121,7 +7127,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7148,7 +7154,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125041757</v>
+        <v>125045722</v>
       </c>
       <c r="B61" t="n">
         <v>78810</v>
@@ -7182,19 +7188,22 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>380887</v>
+        <v>380944</v>
       </c>
       <c r="R61" t="n">
-        <v>6771232</v>
+        <v>6771491</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7223,7 +7232,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7233,7 +7242,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7242,28 +7251,29 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125045722</v>
+        <v>125070201</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7276,40 +7286,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>380944</v>
+        <v>380953</v>
       </c>
       <c r="R62" t="n">
         <v>6771491</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7336,50 +7343,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125041099</v>
+        <v>125050542</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7392,34 +7388,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>380825</v>
+        <v>381332</v>
       </c>
       <c r="R63" t="n">
-        <v>6771235</v>
+        <v>6770903</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7451,7 +7450,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7461,7 +7460,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7470,6 +7469,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125039727</v>
+        <v>125044477</v>
       </c>
       <c r="B64" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7504,37 +7504,40 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Vålviken, Vålviken, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>380927</v>
+        <v>380848</v>
       </c>
       <c r="R64" t="n">
-        <v>6771248</v>
+        <v>6771395</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7563,7 +7566,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7573,7 +7576,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7582,25 +7585,26 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125070202</v>
+        <v>125046579</v>
       </c>
       <c r="B65" t="n">
         <v>78546</v>
@@ -7634,19 +7638,22 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>381352</v>
+        <v>381171</v>
       </c>
       <c r="R65" t="n">
-        <v>6771302</v>
+        <v>6771315</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7673,39 +7680,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125070230</v>
+        <v>125070202</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7718,21 +7736,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7742,10 +7760,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>380964</v>
+        <v>381352</v>
       </c>
       <c r="R66" t="n">
-        <v>6771476</v>
+        <v>6771302</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7804,10 +7822,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125044862</v>
+        <v>125070230</v>
       </c>
       <c r="B67" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7820,37 +7838,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>380803</v>
+        <v>380964</v>
       </c>
       <c r="R67" t="n">
-        <v>6771421</v>
+        <v>6771476</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7880,50 +7895,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125044477</v>
+        <v>125044862</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7936,21 +7940,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7963,13 +7967,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>380848</v>
+        <v>380803</v>
       </c>
       <c r="R68" t="n">
-        <v>6771395</v>
+        <v>6771421</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7998,7 +8002,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8008,7 +8012,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8036,7 +8040,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125046579</v>
+        <v>125039727</v>
       </c>
       <c r="B69" t="n">
         <v>78546</v>
@@ -8070,22 +8074,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Vålviken, Vålviken, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>381171</v>
+        <v>380927</v>
       </c>
       <c r="R69" t="n">
-        <v>6771315</v>
+        <v>6771248</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8114,7 +8115,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8124,7 +8125,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8133,29 +8134,28 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125045234</v>
+        <v>125039513</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8168,40 +8168,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>380888</v>
+        <v>380934</v>
       </c>
       <c r="R70" t="n">
-        <v>6771588</v>
+        <v>6771147</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8230,7 +8227,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8240,7 +8237,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8249,29 +8246,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125041868</v>
+        <v>125045234</v>
       </c>
       <c r="B71" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8284,37 +8280,40 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>380860</v>
+        <v>380888</v>
       </c>
       <c r="R71" t="n">
-        <v>6771171</v>
+        <v>6771588</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8343,7 +8342,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8353,7 +8352,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8362,28 +8361,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125041650</v>
+        <v>125041868</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8396,37 +8396,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>380874</v>
+        <v>380860</v>
       </c>
       <c r="R72" t="n">
-        <v>6771241</v>
+        <v>6771171</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8480,19 +8480,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125070208</v>
+        <v>125041650</v>
       </c>
       <c r="B73" t="n">
         <v>78810</v>
@@ -8528,17 +8528,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>381532</v>
+        <v>380874</v>
       </c>
       <c r="R73" t="n">
-        <v>6771209</v>
+        <v>6771241</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8565,9 +8565,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8582,19 +8592,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125070240</v>
+        <v>125070208</v>
       </c>
       <c r="B74" t="n">
         <v>78810</v>
@@ -8634,10 +8644,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>380912</v>
+        <v>381532</v>
       </c>
       <c r="R74" t="n">
-        <v>6771537</v>
+        <v>6771209</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8696,10 +8706,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125050680</v>
+        <v>125070240</v>
       </c>
       <c r="B75" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8712,37 +8722,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>381264</v>
+        <v>380912</v>
       </c>
       <c r="R75" t="n">
-        <v>6770968</v>
+        <v>6771537</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8772,50 +8779,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125070213</v>
+        <v>125050680</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8828,34 +8824,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>381368</v>
+        <v>381264</v>
       </c>
       <c r="R76" t="n">
-        <v>6771391</v>
+        <v>6770968</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8885,39 +8884,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125070193</v>
+        <v>125070213</v>
       </c>
       <c r="B77" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8930,21 +8940,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8954,10 +8964,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>380811</v>
+        <v>381368</v>
       </c>
       <c r="R77" t="n">
-        <v>6771473</v>
+        <v>6771391</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -9016,10 +9026,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125039513</v>
+        <v>125070193</v>
       </c>
       <c r="B78" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9032,34 +9042,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>380934</v>
+        <v>380811</v>
       </c>
       <c r="R78" t="n">
-        <v>6771147</v>
+        <v>6771473</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -9089,19 +9099,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10101,10 +10101,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125070204</v>
+        <v>125039429</v>
       </c>
       <c r="B88" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10117,34 +10117,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>381311</v>
+        <v>380933</v>
       </c>
       <c r="R88" t="n">
-        <v>6771370</v>
+        <v>6771152</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -10174,9 +10174,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10203,7 +10213,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125070271</v>
+        <v>125045538</v>
       </c>
       <c r="B89" t="n">
         <v>78810</v>
@@ -10237,19 +10247,22 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>380767</v>
+        <v>380927</v>
       </c>
       <c r="R89" t="n">
-        <v>6770999</v>
+        <v>6771538</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10276,39 +10289,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125070205</v>
+        <v>125070200</v>
       </c>
       <c r="B90" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10321,21 +10345,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10345,7 +10369,7 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>380806</v>
+        <v>380812</v>
       </c>
       <c r="R90" t="n">
         <v>6771391</v>
@@ -10407,10 +10431,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125070253</v>
+        <v>125070204</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10423,21 +10447,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10447,10 +10471,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>380966</v>
+        <v>381311</v>
       </c>
       <c r="R91" t="n">
-        <v>6771241</v>
+        <v>6771370</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10509,7 +10533,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125070239</v>
+        <v>125070271</v>
       </c>
       <c r="B92" t="n">
         <v>78810</v>
@@ -10549,10 +10573,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>380922</v>
+        <v>380767</v>
       </c>
       <c r="R92" t="n">
-        <v>6771536</v>
+        <v>6770999</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10611,10 +10635,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125070200</v>
+        <v>125070205</v>
       </c>
       <c r="B93" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10627,21 +10651,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10651,7 +10675,7 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>380812</v>
+        <v>380806</v>
       </c>
       <c r="R93" t="n">
         <v>6771391</v>
@@ -10713,7 +10737,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125039429</v>
+        <v>125070253</v>
       </c>
       <c r="B94" t="n">
         <v>78810</v>
@@ -10749,14 +10773,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>380933</v>
+        <v>380966</v>
       </c>
       <c r="R94" t="n">
-        <v>6771152</v>
+        <v>6771241</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10786,19 +10810,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10825,7 +10839,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125045538</v>
+        <v>125070239</v>
       </c>
       <c r="B95" t="n">
         <v>78810</v>
@@ -10859,22 +10873,19 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>380927</v>
+        <v>380922</v>
       </c>
       <c r="R95" t="n">
-        <v>6771538</v>
+        <v>6771536</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10901,40 +10912,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11869,10 +11869,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125046479</v>
+        <v>125044358</v>
       </c>
       <c r="B105" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11908,17 +11908,17 @@
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>381151</v>
+        <v>380881</v>
       </c>
       <c r="R105" t="n">
-        <v>6771340</v>
+        <v>6771393</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11973,12 +11973,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12333,10 +12333,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125044358</v>
+        <v>125046479</v>
       </c>
       <c r="B109" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12372,17 +12372,17 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>380881</v>
+        <v>381151</v>
       </c>
       <c r="R109" t="n">
-        <v>6771393</v>
+        <v>6771340</v>
       </c>
       <c r="S109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12437,22 +12437,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125070214</v>
+        <v>125048940</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12465,37 +12465,40 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>381359</v>
+        <v>381311</v>
       </c>
       <c r="R110" t="n">
-        <v>6771390</v>
+        <v>6771438</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12522,39 +12525,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125048940</v>
+        <v>125044964</v>
       </c>
       <c r="B111" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12567,21 +12581,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12594,10 +12608,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>381311</v>
+        <v>380889</v>
       </c>
       <c r="R111" t="n">
-        <v>6771438</v>
+        <v>6771526</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12629,7 +12643,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12639,7 +12653,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12660,14 +12674,14 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125044964</v>
+        <v>125048909</v>
       </c>
       <c r="B112" t="n">
         <v>78810</v>
@@ -12710,10 +12724,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>380889</v>
+        <v>381320</v>
       </c>
       <c r="R112" t="n">
-        <v>6771526</v>
+        <v>6771437</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12745,7 +12759,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12755,7 +12769,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12776,17 +12790,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125048909</v>
+        <v>125049533</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12799,21 +12813,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12822,17 +12836,17 @@
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>381320</v>
+        <v>381300</v>
       </c>
       <c r="R113" t="n">
-        <v>6771437</v>
+        <v>6771367</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12861,7 +12875,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12871,7 +12885,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12887,19 +12901,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125049533</v>
+        <v>125049662</v>
       </c>
       <c r="B114" t="n">
         <v>78546</v>
@@ -12938,17 +12952,17 @@
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>381300</v>
+        <v>381341</v>
       </c>
       <c r="R114" t="n">
-        <v>6771367</v>
+        <v>6771287</v>
       </c>
       <c r="S114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12977,7 +12991,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12987,7 +13001,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13003,22 +13017,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125049662</v>
+        <v>125070214</v>
       </c>
       <c r="B115" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13031,40 +13045,37 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>381341</v>
+        <v>381359</v>
       </c>
       <c r="R115" t="n">
-        <v>6771287</v>
+        <v>6771390</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13091,40 +13102,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>16:45</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -13247,7 +13247,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125070211</v>
+        <v>125044939</v>
       </c>
       <c r="B117" t="n">
         <v>78810</v>
@@ -13281,19 +13281,22 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>381359</v>
+        <v>380889</v>
       </c>
       <c r="R117" t="n">
-        <v>6771263</v>
+        <v>6771527</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13320,39 +13323,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125070236</v>
+        <v>125048848</v>
       </c>
       <c r="B118" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13365,37 +13379,40 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>380922</v>
+        <v>381296</v>
       </c>
       <c r="R118" t="n">
-        <v>6771544</v>
+        <v>6771419</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13422,36 +13439,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125070222</v>
+        <v>125070211</v>
       </c>
       <c r="B119" t="n">
         <v>78810</v>
@@ -13491,10 +13519,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>381053</v>
+        <v>381359</v>
       </c>
       <c r="R119" t="n">
-        <v>6771443</v>
+        <v>6771263</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13553,7 +13581,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125070216</v>
+        <v>125070236</v>
       </c>
       <c r="B120" t="n">
         <v>78810</v>
@@ -13593,10 +13621,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>381340</v>
+        <v>380922</v>
       </c>
       <c r="R120" t="n">
-        <v>6771360</v>
+        <v>6771544</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13655,7 +13683,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125044939</v>
+        <v>125070222</v>
       </c>
       <c r="B121" t="n">
         <v>78810</v>
@@ -13689,22 +13717,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>380889</v>
+        <v>381053</v>
       </c>
       <c r="R121" t="n">
-        <v>6771527</v>
+        <v>6771443</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13731,50 +13756,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125048848</v>
+        <v>125070216</v>
       </c>
       <c r="B122" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13787,40 +13801,37 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>381296</v>
+        <v>381340</v>
       </c>
       <c r="R122" t="n">
-        <v>6771419</v>
+        <v>6771360</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13847,40 +13858,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -15405,10 +15405,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125046355</v>
+        <v>125046145</v>
       </c>
       <c r="B137" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15417,46 +15417,41 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>380860</v>
+        <v>381076</v>
       </c>
       <c r="R137" t="n">
-        <v>6771171</v>
+        <v>6771400</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15488,7 +15483,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15498,7 +15493,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15507,28 +15502,29 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125046145</v>
+        <v>125041901</v>
       </c>
       <c r="B138" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15541,40 +15537,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>381076</v>
+        <v>380904</v>
       </c>
       <c r="R138" t="n">
-        <v>6771400</v>
+        <v>6771257</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15603,7 +15596,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15613,7 +15606,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15622,7 +15615,6 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15634,14 +15626,14 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125041901</v>
+        <v>125045458</v>
       </c>
       <c r="B139" t="n">
         <v>78546</v>
@@ -15675,19 +15667,22 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>380904</v>
+        <v>380944</v>
       </c>
       <c r="R139" t="n">
-        <v>6771257</v>
+        <v>6771491</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15716,7 +15711,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15726,7 +15721,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15735,28 +15730,29 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125045458</v>
+        <v>125046355</v>
       </c>
       <c r="B140" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15765,44 +15761,49 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>380944</v>
+        <v>380860</v>
       </c>
       <c r="R140" t="n">
-        <v>6771491</v>
+        <v>6771171</v>
       </c>
       <c r="S140" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15831,7 +15832,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15841,7 +15842,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15850,26 +15851,25 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125040890</v>
+        <v>125070244</v>
       </c>
       <c r="B141" t="n">
         <v>78810</v>
@@ -15905,17 +15905,17 @@
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>380824</v>
+        <v>380850</v>
       </c>
       <c r="R141" t="n">
-        <v>6771234</v>
+        <v>6771542</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15942,19 +15942,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15969,19 +15959,19 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125046257</v>
+        <v>125070245</v>
       </c>
       <c r="B142" t="n">
         <v>78810</v>
@@ -16015,22 +16005,19 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>381041</v>
+        <v>380845</v>
       </c>
       <c r="R142" t="n">
-        <v>6771405</v>
+        <v>6771493</v>
       </c>
       <c r="S142" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16057,47 +16044,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125045265</v>
+        <v>125070215</v>
       </c>
       <c r="B143" t="n">
         <v>78810</v>
@@ -16131,22 +16107,19 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>380928</v>
+        <v>381346</v>
       </c>
       <c r="R143" t="n">
-        <v>6771589</v>
+        <v>6771363</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16173,50 +16146,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125049726</v>
+        <v>125070232</v>
       </c>
       <c r="B144" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16229,40 +16191,37 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>381316</v>
+        <v>380944</v>
       </c>
       <c r="R144" t="n">
-        <v>6771194</v>
+        <v>6771499</v>
       </c>
       <c r="S144" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16289,47 +16248,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>16:46</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>16:46</t>
-        </is>
-      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125045848</v>
+        <v>125070266</v>
       </c>
       <c r="B145" t="n">
         <v>78810</v>
@@ -16363,22 +16311,19 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>380967</v>
+        <v>380889</v>
       </c>
       <c r="R145" t="n">
-        <v>6771519</v>
+        <v>6771552</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16405,50 +16350,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125070244</v>
+        <v>125070206</v>
       </c>
       <c r="B146" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16461,21 +16395,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16485,10 +16419,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>380850</v>
+        <v>380765</v>
       </c>
       <c r="R146" t="n">
-        <v>6771542</v>
+        <v>6771036</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16547,7 +16481,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125070245</v>
+        <v>125040890</v>
       </c>
       <c r="B147" t="n">
         <v>78810</v>
@@ -16583,17 +16517,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>380845</v>
+        <v>380824</v>
       </c>
       <c r="R147" t="n">
-        <v>6771493</v>
+        <v>6771234</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16620,9 +16554,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16637,19 +16581,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125070215</v>
+        <v>125046257</v>
       </c>
       <c r="B148" t="n">
         <v>78810</v>
@@ -16683,19 +16627,22 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>381346</v>
+        <v>381041</v>
       </c>
       <c r="R148" t="n">
-        <v>6771363</v>
+        <v>6771405</v>
       </c>
       <c r="S148" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16722,36 +16669,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125070232</v>
+        <v>125045265</v>
       </c>
       <c r="B149" t="n">
         <v>78810</v>
@@ -16785,19 +16743,22 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>380944</v>
+        <v>380928</v>
       </c>
       <c r="R149" t="n">
-        <v>6771499</v>
+        <v>6771589</v>
       </c>
       <c r="S149" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16824,39 +16785,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125070266</v>
+        <v>125049726</v>
       </c>
       <c r="B150" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16869,37 +16841,40 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>380889</v>
+        <v>381316</v>
       </c>
       <c r="R150" t="n">
-        <v>6771552</v>
+        <v>6771194</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16926,39 +16901,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125070206</v>
+        <v>125045848</v>
       </c>
       <c r="B151" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16971,37 +16957,40 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>380765</v>
+        <v>380967</v>
       </c>
       <c r="R151" t="n">
-        <v>6771036</v>
+        <v>6771519</v>
       </c>
       <c r="S151" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17028,29 +17017,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
@@ -17173,7 +17173,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125044410</v>
+        <v>125070219</v>
       </c>
       <c r="B153" t="n">
         <v>78810</v>
@@ -17207,22 +17207,19 @@
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380860</v>
+        <v>381095</v>
       </c>
       <c r="R153" t="n">
-        <v>6771407</v>
+        <v>6771411</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17249,55 +17246,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>På björk.</t>
-        </is>
-      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125040199</v>
+        <v>125070217</v>
       </c>
       <c r="B154" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17310,40 +17291,37 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380874</v>
+        <v>381320</v>
       </c>
       <c r="R154" t="n">
-        <v>6771199</v>
+        <v>6771356</v>
       </c>
       <c r="S154" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -17370,47 +17348,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125045518</v>
+        <v>125044410</v>
       </c>
       <c r="B155" t="n">
         <v>78810</v>
@@ -17453,10 +17420,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380930</v>
+        <v>380860</v>
       </c>
       <c r="R155" t="n">
-        <v>6771540</v>
+        <v>6771407</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17488,7 +17455,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17498,7 +17465,12 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>På björk.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17526,10 +17498,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125070219</v>
+        <v>125040199</v>
       </c>
       <c r="B156" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17542,37 +17514,40 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>381095</v>
+        <v>380874</v>
       </c>
       <c r="R156" t="n">
-        <v>6771411</v>
+        <v>6771199</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17599,36 +17574,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125070217</v>
+        <v>125045518</v>
       </c>
       <c r="B157" t="n">
         <v>78810</v>
@@ -17662,19 +17648,22 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>381320</v>
+        <v>380930</v>
       </c>
       <c r="R157" t="n">
-        <v>6771356</v>
+        <v>6771540</v>
       </c>
       <c r="S157" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17701,29 +17690,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -18394,10 +18394,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125040931</v>
+        <v>125070249</v>
       </c>
       <c r="B164" t="n">
-        <v>77738</v>
+        <v>78810</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18410,40 +18410,37 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
         <v>380872</v>
       </c>
       <c r="R164" t="n">
-        <v>6771195</v>
+        <v>6771395</v>
       </c>
       <c r="S164" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18470,50 +18467,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125039976</v>
+        <v>125040931</v>
       </c>
       <c r="B165" t="n">
-        <v>79428</v>
+        <v>77738</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18526,21 +18512,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18553,10 +18539,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380856</v>
+        <v>380872</v>
       </c>
       <c r="R165" t="n">
-        <v>6771167</v>
+        <v>6771195</v>
       </c>
       <c r="S165" t="n">
         <v>9</v>
@@ -18588,7 +18574,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18598,7 +18584,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18626,10 +18612,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125044489</v>
+        <v>125039976</v>
       </c>
       <c r="B166" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18642,21 +18628,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18669,13 +18655,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380835</v>
+        <v>380856</v>
       </c>
       <c r="R166" t="n">
-        <v>6771422</v>
+        <v>6771167</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18704,7 +18690,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18714,7 +18700,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18730,19 +18716,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125070249</v>
+        <v>125044489</v>
       </c>
       <c r="B167" t="n">
         <v>78810</v>
@@ -18776,19 +18762,22 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380872</v>
+        <v>380835</v>
       </c>
       <c r="R167" t="n">
-        <v>6771395</v>
+        <v>6771422</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18815,39 +18804,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125049428</v>
+        <v>125042523</v>
       </c>
       <c r="B168" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18860,21 +18860,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18887,10 +18887,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>381345</v>
+        <v>381014</v>
       </c>
       <c r="R168" t="n">
-        <v>6771402</v>
+        <v>6771206</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18932,7 +18932,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18953,17 +18953,17 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125070260</v>
+        <v>125046556</v>
       </c>
       <c r="B169" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18976,37 +18976,40 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380775</v>
+        <v>381175</v>
       </c>
       <c r="R169" t="n">
-        <v>6771061</v>
+        <v>6771338</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19033,39 +19036,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125042523</v>
+        <v>125049428</v>
       </c>
       <c r="B170" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19078,21 +19092,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19105,10 +19119,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>381014</v>
+        <v>381345</v>
       </c>
       <c r="R170" t="n">
-        <v>6771206</v>
+        <v>6771402</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19140,7 +19154,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19150,7 +19164,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19171,17 +19185,17 @@
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125046556</v>
+        <v>125070260</v>
       </c>
       <c r="B171" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -19194,40 +19208,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>381175</v>
+        <v>380775</v>
       </c>
       <c r="R171" t="n">
-        <v>6771338</v>
+        <v>6771061</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19254,50 +19265,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125070224</v>
+        <v>125050455</v>
       </c>
       <c r="B172" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19310,37 +19310,40 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>381027</v>
+        <v>381361</v>
       </c>
       <c r="R172" t="n">
-        <v>6771451</v>
+        <v>6770935</v>
       </c>
       <c r="S172" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19367,36 +19370,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125070247</v>
+        <v>125070224</v>
       </c>
       <c r="B173" t="n">
         <v>78810</v>
@@ -19436,10 +19450,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>380827</v>
+        <v>381027</v>
       </c>
       <c r="R173" t="n">
-        <v>6771384</v>
+        <v>6771451</v>
       </c>
       <c r="S173" t="n">
         <v>15</v>
@@ -19498,10 +19512,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125050455</v>
+        <v>125070247</v>
       </c>
       <c r="B174" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19514,40 +19528,37 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>381361</v>
+        <v>380827</v>
       </c>
       <c r="R174" t="n">
-        <v>6770935</v>
+        <v>6771384</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19574,50 +19585,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125040971</v>
+        <v>125044547</v>
       </c>
       <c r="B175" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19630,37 +19630,40 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380824</v>
+        <v>380821</v>
       </c>
       <c r="R175" t="n">
-        <v>6771235</v>
+        <v>6771374</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19689,7 +19692,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19699,7 +19702,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19708,28 +19711,29 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125044547</v>
+        <v>125040971</v>
       </c>
       <c r="B176" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19742,40 +19746,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380821</v>
+        <v>380824</v>
       </c>
       <c r="R176" t="n">
-        <v>6771374</v>
+        <v>6771235</v>
       </c>
       <c r="S176" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19804,7 +19805,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19814,7 +19815,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19823,19 +19824,18 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -3136,10 +3136,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125040653</v>
+        <v>125070241</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3152,40 +3152,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>380872</v>
+        <v>380908</v>
       </c>
       <c r="R24" t="n">
-        <v>6771195</v>
+        <v>6771533</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3212,50 +3209,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125040326</v>
+        <v>125070261</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3268,37 +3254,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380824</v>
+        <v>381036</v>
       </c>
       <c r="R25" t="n">
-        <v>6771177</v>
+        <v>6771447</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3325,19 +3311,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3352,22 +3328,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125049457</v>
+        <v>125070256</v>
       </c>
       <c r="B26" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3380,34 +3356,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>380860</v>
+        <v>380801</v>
       </c>
       <c r="R26" t="n">
-        <v>6771171</v>
+        <v>6771192</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3437,19 +3413,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:36</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,19 +3430,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125070241</v>
+        <v>125070218</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3516,10 +3482,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380908</v>
+        <v>381266</v>
       </c>
       <c r="R27" t="n">
-        <v>6771533</v>
+        <v>6771351</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3578,7 +3544,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125070261</v>
+        <v>125070227</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3618,10 +3584,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>381036</v>
+        <v>380995</v>
       </c>
       <c r="R28" t="n">
-        <v>6771447</v>
+        <v>6771436</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3680,7 +3646,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125070256</v>
+        <v>125070238</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3720,10 +3686,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380801</v>
+        <v>380917</v>
       </c>
       <c r="R29" t="n">
-        <v>6771192</v>
+        <v>6771547</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3782,10 +3748,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125070218</v>
+        <v>125040653</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3798,37 +3764,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>381266</v>
+        <v>380872</v>
       </c>
       <c r="R30" t="n">
-        <v>6771351</v>
+        <v>6771195</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3855,39 +3824,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125070227</v>
+        <v>125040326</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3900,37 +3880,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380995</v>
+        <v>380824</v>
       </c>
       <c r="R31" t="n">
-        <v>6771436</v>
+        <v>6771177</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3957,9 +3937,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3974,22 +3964,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125070238</v>
+        <v>125049457</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4002,34 +3992,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380917</v>
+        <v>380860</v>
       </c>
       <c r="R32" t="n">
-        <v>6771547</v>
+        <v>6771171</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4059,9 +4049,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4076,22 +4076,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125046270</v>
+        <v>125070203</v>
       </c>
       <c r="B33" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4104,40 +4104,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>381095</v>
+        <v>381386</v>
       </c>
       <c r="R33" t="n">
-        <v>6771385</v>
+        <v>6771403</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4164,50 +4161,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125049925</v>
+        <v>125070250</v>
       </c>
       <c r="B34" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4220,40 +4206,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>381316</v>
+        <v>380990</v>
       </c>
       <c r="R34" t="n">
-        <v>6771194</v>
+        <v>6771182</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4280,50 +4263,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125047288</v>
+        <v>125070269</v>
       </c>
       <c r="B35" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4336,40 +4308,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>381041</v>
+        <v>380938</v>
       </c>
       <c r="R35" t="n">
-        <v>6771405</v>
+        <v>6771234</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4396,40 +4365,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4552,10 +4510,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125070203</v>
+        <v>125046270</v>
       </c>
       <c r="B37" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4568,37 +4526,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>381386</v>
+        <v>381095</v>
       </c>
       <c r="R37" t="n">
-        <v>6771403</v>
+        <v>6771385</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4625,39 +4586,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125070250</v>
+        <v>125049925</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4670,37 +4642,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>380990</v>
+        <v>381316</v>
       </c>
       <c r="R38" t="n">
-        <v>6771182</v>
+        <v>6771194</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4727,39 +4702,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125070269</v>
+        <v>125047288</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4772,37 +4758,40 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>380938</v>
+        <v>381041</v>
       </c>
       <c r="R39" t="n">
-        <v>6771234</v>
+        <v>6771405</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4829,29 +4818,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -7488,10 +7488,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125044477</v>
+        <v>125039727</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7504,40 +7504,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Vålviken, Vålviken, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>380848</v>
+        <v>380927</v>
       </c>
       <c r="R64" t="n">
-        <v>6771395</v>
+        <v>6771248</v>
       </c>
       <c r="S64" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7566,7 +7563,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7576,7 +7573,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7585,29 +7582,28 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125046579</v>
+        <v>125044477</v>
       </c>
       <c r="B65" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7620,21 +7616,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7643,17 +7639,17 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>381171</v>
+        <v>380848</v>
       </c>
       <c r="R65" t="n">
-        <v>6771315</v>
+        <v>6771395</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7682,7 +7678,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7692,7 +7688,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7708,19 +7704,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125070202</v>
+        <v>125046579</v>
       </c>
       <c r="B66" t="n">
         <v>78546</v>
@@ -7754,19 +7750,22 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>381352</v>
+        <v>381171</v>
       </c>
       <c r="R66" t="n">
-        <v>6771302</v>
+        <v>6771315</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7793,39 +7792,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125070230</v>
+        <v>125044862</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7838,34 +7848,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>380964</v>
+        <v>380803</v>
       </c>
       <c r="R67" t="n">
-        <v>6771476</v>
+        <v>6771421</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7895,39 +7908,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125044862</v>
+        <v>125070202</v>
       </c>
       <c r="B68" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7940,37 +7964,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>380803</v>
+        <v>381352</v>
       </c>
       <c r="R68" t="n">
-        <v>6771421</v>
+        <v>6771302</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8000,50 +8021,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125039727</v>
+        <v>125070230</v>
       </c>
       <c r="B69" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8056,34 +8066,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vålviken, Vålviken, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>380927</v>
+        <v>380964</v>
       </c>
       <c r="R69" t="n">
-        <v>6771248</v>
+        <v>6771476</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8113,19 +8123,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -11869,10 +11869,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125044358</v>
+        <v>125046479</v>
       </c>
       <c r="B105" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11885,21 +11885,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11908,17 +11908,17 @@
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>380881</v>
+        <v>381151</v>
       </c>
       <c r="R105" t="n">
-        <v>6771393</v>
+        <v>6771340</v>
       </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11973,12 +11973,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12333,10 +12333,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125046479</v>
+        <v>125044358</v>
       </c>
       <c r="B109" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12349,21 +12349,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12372,17 +12372,17 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>381151</v>
+        <v>380881</v>
       </c>
       <c r="R109" t="n">
-        <v>6771340</v>
+        <v>6771393</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12437,12 +12437,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -15405,10 +15405,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125046145</v>
+        <v>125046355</v>
       </c>
       <c r="B137" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15417,41 +15417,46 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>381076</v>
+        <v>380860</v>
       </c>
       <c r="R137" t="n">
-        <v>6771400</v>
+        <v>6771171</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15483,7 +15488,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15493,7 +15498,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15502,29 +15507,28 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125041901</v>
+        <v>125046145</v>
       </c>
       <c r="B138" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15537,37 +15541,40 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>380904</v>
+        <v>381076</v>
       </c>
       <c r="R138" t="n">
-        <v>6771257</v>
+        <v>6771400</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15596,7 +15603,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15606,7 +15613,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15615,6 +15622,7 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -15626,14 +15634,14 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125045458</v>
+        <v>125041901</v>
       </c>
       <c r="B139" t="n">
         <v>78546</v>
@@ -15667,22 +15675,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>380944</v>
+        <v>380904</v>
       </c>
       <c r="R139" t="n">
-        <v>6771491</v>
+        <v>6771257</v>
       </c>
       <c r="S139" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15711,7 +15716,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15721,7 +15726,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15730,29 +15735,28 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125046355</v>
+        <v>125045458</v>
       </c>
       <c r="B140" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15761,49 +15765,44 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>380860</v>
+        <v>380944</v>
       </c>
       <c r="R140" t="n">
-        <v>6771171</v>
+        <v>6771491</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15832,7 +15831,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15842,7 +15841,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15851,28 +15850,29 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125070244</v>
+        <v>125045567</v>
       </c>
       <c r="B141" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15885,37 +15885,40 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>380850</v>
+        <v>380944</v>
       </c>
       <c r="R141" t="n">
-        <v>6771542</v>
+        <v>6771491</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15942,36 +15945,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125070245</v>
+        <v>125040890</v>
       </c>
       <c r="B142" t="n">
         <v>78810</v>
@@ -16007,17 +16021,17 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>380845</v>
+        <v>380824</v>
       </c>
       <c r="R142" t="n">
-        <v>6771493</v>
+        <v>6771234</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16044,9 +16058,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16061,19 +16085,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125070215</v>
+        <v>125046257</v>
       </c>
       <c r="B143" t="n">
         <v>78810</v>
@@ -16107,19 +16131,22 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>381346</v>
+        <v>381041</v>
       </c>
       <c r="R143" t="n">
-        <v>6771363</v>
+        <v>6771405</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16146,36 +16173,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125070232</v>
+        <v>125045265</v>
       </c>
       <c r="B144" t="n">
         <v>78810</v>
@@ -16209,19 +16247,22 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>380944</v>
+        <v>380928</v>
       </c>
       <c r="R144" t="n">
-        <v>6771499</v>
+        <v>6771589</v>
       </c>
       <c r="S144" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16248,39 +16289,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125070266</v>
+        <v>125049726</v>
       </c>
       <c r="B145" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16293,37 +16345,40 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>380889</v>
+        <v>381316</v>
       </c>
       <c r="R145" t="n">
-        <v>6771552</v>
+        <v>6771194</v>
       </c>
       <c r="S145" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16350,39 +16405,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125070206</v>
+        <v>125045848</v>
       </c>
       <c r="B146" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16395,37 +16461,40 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>380765</v>
+        <v>380967</v>
       </c>
       <c r="R146" t="n">
-        <v>6771036</v>
+        <v>6771519</v>
       </c>
       <c r="S146" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16452,36 +16521,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125040890</v>
+        <v>125070244</v>
       </c>
       <c r="B147" t="n">
         <v>78810</v>
@@ -16517,17 +16597,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>380824</v>
+        <v>380850</v>
       </c>
       <c r="R147" t="n">
-        <v>6771234</v>
+        <v>6771542</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16554,19 +16634,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16581,19 +16651,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125046257</v>
+        <v>125070245</v>
       </c>
       <c r="B148" t="n">
         <v>78810</v>
@@ -16627,22 +16697,19 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>381041</v>
+        <v>380845</v>
       </c>
       <c r="R148" t="n">
-        <v>6771405</v>
+        <v>6771493</v>
       </c>
       <c r="S148" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16669,47 +16736,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125045265</v>
+        <v>125070215</v>
       </c>
       <c r="B149" t="n">
         <v>78810</v>
@@ -16743,22 +16799,19 @@
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>380928</v>
+        <v>381346</v>
       </c>
       <c r="R149" t="n">
-        <v>6771589</v>
+        <v>6771363</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16785,50 +16838,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125049726</v>
+        <v>125070232</v>
       </c>
       <c r="B150" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16841,40 +16883,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>381316</v>
+        <v>380944</v>
       </c>
       <c r="R150" t="n">
-        <v>6771194</v>
+        <v>6771499</v>
       </c>
       <c r="S150" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16901,47 +16940,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>16:46</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>16:46</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125045848</v>
+        <v>125070266</v>
       </c>
       <c r="B151" t="n">
         <v>78810</v>
@@ -16975,22 +17003,19 @@
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>380967</v>
+        <v>380889</v>
       </c>
       <c r="R151" t="n">
-        <v>6771519</v>
+        <v>6771552</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17017,50 +17042,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AD151" t="b">
         <v>0</v>
       </c>
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125045567</v>
+        <v>125070206</v>
       </c>
       <c r="B152" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -17073,40 +17087,37 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380944</v>
+        <v>380765</v>
       </c>
       <c r="R152" t="n">
-        <v>6771491</v>
+        <v>6771036</v>
       </c>
       <c r="S152" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17133,40 +17144,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AD152" t="b">
         <v>0</v>
       </c>
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
@@ -17730,10 +17730,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125070243</v>
+        <v>125044233</v>
       </c>
       <c r="B158" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17746,37 +17746,40 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380887</v>
+        <v>380900</v>
       </c>
       <c r="R158" t="n">
-        <v>6771552</v>
+        <v>6771401</v>
       </c>
       <c r="S158" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17803,36 +17806,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125040078</v>
+        <v>125070243</v>
       </c>
       <c r="B159" t="n">
         <v>78810</v>
@@ -17868,14 +17882,14 @@
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380836</v>
+        <v>380887</v>
       </c>
       <c r="R159" t="n">
-        <v>6771174</v>
+        <v>6771552</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -17905,19 +17919,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17932,22 +17936,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125044233</v>
+        <v>125040078</v>
       </c>
       <c r="B160" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17960,40 +17964,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380900</v>
+        <v>380836</v>
       </c>
       <c r="R160" t="n">
-        <v>6771401</v>
+        <v>6771174</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18022,7 +18023,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18032,7 +18033,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18041,7 +18042,6 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -18053,7 +18053,7 @@
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -18394,10 +18394,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125070249</v>
+        <v>125040931</v>
       </c>
       <c r="B164" t="n">
-        <v>78810</v>
+        <v>77738</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18410,37 +18410,40 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
         <v>380872</v>
       </c>
       <c r="R164" t="n">
-        <v>6771395</v>
+        <v>6771195</v>
       </c>
       <c r="S164" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18467,39 +18470,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125040931</v>
+        <v>125039976</v>
       </c>
       <c r="B165" t="n">
-        <v>77738</v>
+        <v>79428</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18512,21 +18526,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18539,10 +18553,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380872</v>
+        <v>380856</v>
       </c>
       <c r="R165" t="n">
-        <v>6771195</v>
+        <v>6771167</v>
       </c>
       <c r="S165" t="n">
         <v>9</v>
@@ -18574,7 +18588,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18584,7 +18598,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18612,10 +18626,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125039976</v>
+        <v>125044489</v>
       </c>
       <c r="B166" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18628,21 +18642,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18655,13 +18669,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380856</v>
+        <v>380835</v>
       </c>
       <c r="R166" t="n">
-        <v>6771167</v>
+        <v>6771422</v>
       </c>
       <c r="S166" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18690,7 +18704,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18700,7 +18714,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18716,19 +18730,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125044489</v>
+        <v>125070249</v>
       </c>
       <c r="B167" t="n">
         <v>78810</v>
@@ -18762,22 +18776,19 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380835</v>
+        <v>380872</v>
       </c>
       <c r="R167" t="n">
-        <v>6771422</v>
+        <v>6771395</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18804,40 +18815,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
@@ -19294,10 +19294,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125050455</v>
+        <v>125070224</v>
       </c>
       <c r="B172" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19310,40 +19310,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>381361</v>
+        <v>381027</v>
       </c>
       <c r="R172" t="n">
-        <v>6770935</v>
+        <v>6771451</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19370,47 +19367,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AD172" t="b">
         <v>0</v>
       </c>
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125070224</v>
+        <v>125070247</v>
       </c>
       <c r="B173" t="n">
         <v>78810</v>
@@ -19450,10 +19436,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>381027</v>
+        <v>380827</v>
       </c>
       <c r="R173" t="n">
-        <v>6771451</v>
+        <v>6771384</v>
       </c>
       <c r="S173" t="n">
         <v>15</v>
@@ -19512,10 +19498,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>125070247</v>
+        <v>125050455</v>
       </c>
       <c r="B174" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19528,37 +19514,40 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>380827</v>
+        <v>381361</v>
       </c>
       <c r="R174" t="n">
-        <v>6771384</v>
+        <v>6770935</v>
       </c>
       <c r="S174" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19585,39 +19574,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>125044547</v>
+        <v>125040971</v>
       </c>
       <c r="B175" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19630,40 +19630,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>380821</v>
+        <v>380824</v>
       </c>
       <c r="R175" t="n">
-        <v>6771374</v>
+        <v>6771235</v>
       </c>
       <c r="S175" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19692,7 +19689,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19702,7 +19699,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19711,29 +19708,28 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>125040971</v>
+        <v>125044547</v>
       </c>
       <c r="B176" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19746,37 +19742,40 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>380824</v>
+        <v>380821</v>
       </c>
       <c r="R176" t="n">
-        <v>6771235</v>
+        <v>6771374</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19805,7 +19804,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19815,7 +19814,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19824,18 +19823,19 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -4240,7 +4240,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125045518</v>
+        <v>125044246</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4283,13 +4283,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380930</v>
+        <v>380900</v>
       </c>
       <c r="R34" t="n">
-        <v>6771540</v>
+        <v>6771401</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4356,7 +4356,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125044246</v>
+        <v>125070248</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4390,19 +4390,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380900</v>
+        <v>380858</v>
       </c>
       <c r="R35" t="n">
-        <v>6771401</v>
+        <v>6771400</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4432,47 +4429,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125070248</v>
+        <v>125070228</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4512,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>380858</v>
+        <v>380972</v>
       </c>
       <c r="R36" t="n">
-        <v>6771400</v>
+        <v>6771478</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4574,7 +4560,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125070228</v>
+        <v>125070267</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4614,10 +4600,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>380972</v>
+        <v>380852</v>
       </c>
       <c r="R37" t="n">
-        <v>6771478</v>
+        <v>6771474</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4676,7 +4662,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125070267</v>
+        <v>125045518</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4710,19 +4696,22 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>380852</v>
+        <v>380930</v>
       </c>
       <c r="R38" t="n">
-        <v>6771474</v>
+        <v>6771540</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4749,29 +4738,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4890,10 +4890,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125044477</v>
+        <v>125070191</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4906,40 +4906,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>380848</v>
+        <v>380812</v>
       </c>
       <c r="R40" t="n">
-        <v>6771395</v>
+        <v>6771477</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4966,47 +4963,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125046257</v>
+        <v>125044477</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -5049,10 +5035,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>381041</v>
+        <v>380848</v>
       </c>
       <c r="R41" t="n">
-        <v>6771405</v>
+        <v>6771395</v>
       </c>
       <c r="S41" t="n">
         <v>8</v>
@@ -5084,7 +5070,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5094,7 +5080,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5122,10 +5108,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125046107</v>
+        <v>125046257</v>
       </c>
       <c r="B42" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5138,37 +5124,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>380860</v>
+        <v>381041</v>
       </c>
       <c r="R42" t="n">
-        <v>6771171</v>
+        <v>6771405</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5197,7 +5186,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5207,7 +5196,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5216,28 +5205,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125070191</v>
+        <v>125046107</v>
       </c>
       <c r="B43" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5250,34 +5240,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>380812</v>
+        <v>380860</v>
       </c>
       <c r="R43" t="n">
-        <v>6771477</v>
+        <v>6771171</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5307,9 +5297,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5324,12 +5324,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125041141</v>
+        <v>125070264</v>
       </c>
       <c r="B78" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9090,37 +9090,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>380828</v>
+        <v>380899</v>
       </c>
       <c r="R78" t="n">
-        <v>6771239</v>
+        <v>6771529</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9147,19 +9147,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9174,22 +9164,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125039976</v>
+        <v>125050078</v>
       </c>
       <c r="B79" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9202,21 +9192,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9225,14 +9215,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>380856</v>
+        <v>381316</v>
       </c>
       <c r="R79" t="n">
-        <v>6771167</v>
+        <v>6771194</v>
       </c>
       <c r="S79" t="n">
         <v>9</v>
@@ -9264,7 +9254,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9274,7 +9264,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9302,10 +9292,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125046449</v>
+        <v>125070219</v>
       </c>
       <c r="B80" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9318,34 +9308,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>380860</v>
+        <v>381095</v>
       </c>
       <c r="R80" t="n">
-        <v>6771171</v>
+        <v>6771411</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9375,19 +9365,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9402,22 +9382,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125041901</v>
+        <v>125070241</v>
       </c>
       <c r="B81" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9430,37 +9410,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>380904</v>
+        <v>380908</v>
       </c>
       <c r="R81" t="n">
-        <v>6771257</v>
+        <v>6771533</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9487,19 +9467,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9514,22 +9484,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125070264</v>
+        <v>125050680</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9542,34 +9512,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>380899</v>
+        <v>381264</v>
       </c>
       <c r="R82" t="n">
-        <v>6771529</v>
+        <v>6770968</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9599,39 +9572,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125050078</v>
+        <v>125070203</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9644,40 +9628,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>381316</v>
+        <v>381386</v>
       </c>
       <c r="R83" t="n">
-        <v>6771194</v>
+        <v>6771403</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9704,50 +9685,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>16:57</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125070219</v>
+        <v>125044233</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9760,37 +9730,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>381095</v>
+        <v>380900</v>
       </c>
       <c r="R84" t="n">
-        <v>6771411</v>
+        <v>6771401</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9817,39 +9790,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125070241</v>
+        <v>125041141</v>
       </c>
       <c r="B85" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9862,37 +9846,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>380908</v>
+        <v>380828</v>
       </c>
       <c r="R85" t="n">
-        <v>6771533</v>
+        <v>6771239</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9919,9 +9903,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9936,22 +9930,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125050680</v>
+        <v>125039976</v>
       </c>
       <c r="B86" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9964,21 +9958,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9991,13 +9985,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>381264</v>
+        <v>380856</v>
       </c>
       <c r="R86" t="n">
-        <v>6770968</v>
+        <v>6771167</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10026,7 +10020,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10036,7 +10030,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10052,19 +10046,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125070203</v>
+        <v>125046449</v>
       </c>
       <c r="B87" t="n">
         <v>78546</v>
@@ -10100,14 +10094,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>381386</v>
+        <v>380860</v>
       </c>
       <c r="R87" t="n">
-        <v>6771403</v>
+        <v>6771171</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -10137,9 +10131,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10154,22 +10158,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125045848</v>
+        <v>125041901</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10182,37 +10186,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>380967</v>
+        <v>380904</v>
       </c>
       <c r="R88" t="n">
-        <v>6771519</v>
+        <v>6771257</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10244,7 +10245,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10254,7 +10255,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10263,7 +10264,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10275,14 +10275,14 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125046096</v>
+        <v>125045848</v>
       </c>
       <c r="B89" t="n">
         <v>78810</v>
@@ -10321,17 +10321,17 @@
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>381038</v>
+        <v>380967</v>
       </c>
       <c r="R89" t="n">
-        <v>6771446</v>
+        <v>6771519</v>
       </c>
       <c r="S89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10386,22 +10386,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125070200</v>
+        <v>125046096</v>
       </c>
       <c r="B90" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10414,37 +10414,40 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>380812</v>
+        <v>381038</v>
       </c>
       <c r="R90" t="n">
-        <v>6771391</v>
+        <v>6771446</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10471,36 +10474,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125044233</v>
+        <v>125070200</v>
       </c>
       <c r="B91" t="n">
         <v>78547</v>
@@ -10534,22 +10548,19 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>380900</v>
+        <v>380812</v>
       </c>
       <c r="R91" t="n">
-        <v>6771401</v>
+        <v>6771391</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10576,50 +10587,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125070207</v>
+        <v>125046088</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10632,37 +10632,40 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>381296</v>
+        <v>381037</v>
       </c>
       <c r="R92" t="n">
-        <v>6771103</v>
+        <v>6771430</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10689,39 +10692,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125046088</v>
+        <v>125044979</v>
       </c>
       <c r="B93" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10734,21 +10748,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10761,10 +10775,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>381037</v>
+        <v>380890</v>
       </c>
       <c r="R93" t="n">
-        <v>6771430</v>
+        <v>6771528</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10796,7 +10810,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10806,7 +10820,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10827,14 +10841,14 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125044979</v>
+        <v>125045722</v>
       </c>
       <c r="B94" t="n">
         <v>78810</v>
@@ -10873,17 +10887,17 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>380890</v>
+        <v>380944</v>
       </c>
       <c r="R94" t="n">
-        <v>6771528</v>
+        <v>6771491</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10912,7 +10926,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10922,7 +10936,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10938,19 +10952,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125045722</v>
+        <v>125070207</v>
       </c>
       <c r="B95" t="n">
         <v>78810</v>
@@ -10984,22 +10998,19 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>380944</v>
+        <v>381296</v>
       </c>
       <c r="R95" t="n">
-        <v>6771491</v>
+        <v>6771103</v>
       </c>
       <c r="S95" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11026,40 +11037,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11515,7 +11515,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125070215</v>
+        <v>125040302</v>
       </c>
       <c r="B100" t="n">
         <v>78810</v>
@@ -11551,17 +11551,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>381346</v>
+        <v>380817</v>
       </c>
       <c r="R100" t="n">
-        <v>6771363</v>
+        <v>6771175</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11588,9 +11588,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11605,19 +11615,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125070256</v>
+        <v>125049404</v>
       </c>
       <c r="B101" t="n">
         <v>78810</v>
@@ -11651,19 +11661,22 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>380801</v>
+        <v>381342</v>
       </c>
       <c r="R101" t="n">
-        <v>6771192</v>
+        <v>6771402</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11690,36 +11703,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125040302</v>
+        <v>125045538</v>
       </c>
       <c r="B102" t="n">
         <v>78810</v>
@@ -11753,16 +11777,19 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>380817</v>
+        <v>380927</v>
       </c>
       <c r="R102" t="n">
-        <v>6771175</v>
+        <v>6771538</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11794,7 +11821,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11804,7 +11831,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11813,6 +11840,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11824,14 +11852,14 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125049404</v>
+        <v>125044513</v>
       </c>
       <c r="B103" t="n">
         <v>78810</v>
@@ -11874,10 +11902,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>381342</v>
+        <v>380828</v>
       </c>
       <c r="R103" t="n">
-        <v>6771402</v>
+        <v>6771432</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11909,7 +11937,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11919,7 +11947,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11940,14 +11968,14 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125045538</v>
+        <v>125040000</v>
       </c>
       <c r="B104" t="n">
         <v>78810</v>
@@ -11981,22 +12009,19 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>380927</v>
+        <v>380848</v>
       </c>
       <c r="R104" t="n">
-        <v>6771538</v>
+        <v>6771174</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12025,7 +12050,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12035,7 +12060,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12044,7 +12069,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12056,17 +12080,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125044513</v>
+        <v>125046355</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12075,44 +12099,49 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>380828</v>
+        <v>380860</v>
       </c>
       <c r="R105" t="n">
-        <v>6771432</v>
+        <v>6771171</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12141,7 +12170,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12151,7 +12180,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12160,29 +12189,28 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125040000</v>
+        <v>125047288</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12195,37 +12223,40 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>380848</v>
+        <v>381041</v>
       </c>
       <c r="R106" t="n">
-        <v>6771174</v>
+        <v>6771405</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12254,7 +12285,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12264,7 +12295,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12273,28 +12304,29 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125046355</v>
+        <v>125070215</v>
       </c>
       <c r="B107" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12303,46 +12335,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>380860</v>
+        <v>381346</v>
       </c>
       <c r="R107" t="n">
-        <v>6771171</v>
+        <v>6771363</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -12372,19 +12396,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12399,22 +12413,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125047288</v>
+        <v>125070256</v>
       </c>
       <c r="B108" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12427,40 +12441,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>381041</v>
+        <v>380801</v>
       </c>
       <c r="R108" t="n">
-        <v>6771405</v>
+        <v>6771192</v>
       </c>
       <c r="S108" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12487,40 +12498,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13863,10 +13863,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125048848</v>
+        <v>125070242</v>
       </c>
       <c r="B121" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13879,40 +13879,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>381296</v>
+        <v>380901</v>
       </c>
       <c r="R121" t="n">
-        <v>6771419</v>
+        <v>6771508</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13939,47 +13936,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125070242</v>
+        <v>125070212</v>
       </c>
       <c r="B122" t="n">
         <v>78810</v>
@@ -14019,10 +14005,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>380901</v>
+        <v>381311</v>
       </c>
       <c r="R122" t="n">
-        <v>6771508</v>
+        <v>6771289</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -14081,7 +14067,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125070212</v>
+        <v>125070227</v>
       </c>
       <c r="B123" t="n">
         <v>78810</v>
@@ -14121,10 +14107,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>381311</v>
+        <v>380995</v>
       </c>
       <c r="R123" t="n">
-        <v>6771289</v>
+        <v>6771436</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -14183,10 +14169,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125070227</v>
+        <v>125046270</v>
       </c>
       <c r="B124" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14199,37 +14185,40 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>380995</v>
+        <v>381095</v>
       </c>
       <c r="R124" t="n">
-        <v>6771436</v>
+        <v>6771385</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14256,39 +14245,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125039429</v>
+        <v>125048848</v>
       </c>
       <c r="B125" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14301,37 +14301,40 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>380933</v>
+        <v>381296</v>
       </c>
       <c r="R125" t="n">
-        <v>6771152</v>
+        <v>6771419</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14360,7 +14363,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14370,7 +14373,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14379,28 +14382,29 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125049925</v>
+        <v>125039429</v>
       </c>
       <c r="B126" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14413,40 +14417,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>381316</v>
+        <v>380933</v>
       </c>
       <c r="R126" t="n">
-        <v>6771194</v>
+        <v>6771152</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14475,7 +14476,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14485,7 +14486,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14494,26 +14495,25 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125046270</v>
+        <v>125049925</v>
       </c>
       <c r="B127" t="n">
         <v>78547</v>
@@ -14552,14 +14552,14 @@
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>381095</v>
+        <v>381316</v>
       </c>
       <c r="R127" t="n">
-        <v>6771385</v>
+        <v>6771194</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14617,12 +14617,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -14741,7 +14741,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125041900</v>
+        <v>125070210</v>
       </c>
       <c r="B129" t="n">
         <v>78810</v>
@@ -14775,22 +14775,19 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>380872</v>
+        <v>381370</v>
       </c>
       <c r="R129" t="n">
-        <v>6771195</v>
+        <v>6771255</v>
       </c>
       <c r="S129" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14817,47 +14814,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125070210</v>
+        <v>125070216</v>
       </c>
       <c r="B130" t="n">
         <v>78810</v>
@@ -14897,10 +14883,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>381370</v>
+        <v>381340</v>
       </c>
       <c r="R130" t="n">
-        <v>6771255</v>
+        <v>6771360</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14959,7 +14945,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125070216</v>
+        <v>125041900</v>
       </c>
       <c r="B131" t="n">
         <v>78810</v>
@@ -14993,19 +14979,22 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>381340</v>
+        <v>380872</v>
       </c>
       <c r="R131" t="n">
-        <v>6771360</v>
+        <v>6771195</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15032,29 +15021,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -16866,10 +16866,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125040971</v>
+        <v>125070245</v>
       </c>
       <c r="B149" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16882,37 +16882,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>380824</v>
+        <v>380845</v>
       </c>
       <c r="R149" t="n">
-        <v>6771235</v>
+        <v>6771493</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16939,19 +16939,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16966,22 +16956,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125040199</v>
+        <v>125070234</v>
       </c>
       <c r="B150" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16994,40 +16984,37 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>380874</v>
+        <v>380940</v>
       </c>
       <c r="R150" t="n">
-        <v>6771199</v>
+        <v>6771511</v>
       </c>
       <c r="S150" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17054,47 +17041,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD150" t="b">
         <v>0</v>
       </c>
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125070245</v>
+        <v>125070255</v>
       </c>
       <c r="B151" t="n">
         <v>78810</v>
@@ -17134,10 +17110,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>380845</v>
+        <v>380893</v>
       </c>
       <c r="R151" t="n">
-        <v>6771493</v>
+        <v>6771236</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -17196,7 +17172,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125070234</v>
+        <v>125070231</v>
       </c>
       <c r="B152" t="n">
         <v>78810</v>
@@ -17236,10 +17212,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380940</v>
+        <v>380946</v>
       </c>
       <c r="R152" t="n">
-        <v>6771511</v>
+        <v>6771491</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -17298,7 +17274,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125070255</v>
+        <v>125070235</v>
       </c>
       <c r="B153" t="n">
         <v>78810</v>
@@ -17338,10 +17314,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>380893</v>
+        <v>380941</v>
       </c>
       <c r="R153" t="n">
-        <v>6771236</v>
+        <v>6771522</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -17400,7 +17376,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125070231</v>
+        <v>125070222</v>
       </c>
       <c r="B154" t="n">
         <v>78810</v>
@@ -17440,10 +17416,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>380946</v>
+        <v>381053</v>
       </c>
       <c r="R154" t="n">
-        <v>6771491</v>
+        <v>6771443</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17502,10 +17478,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125070235</v>
+        <v>125040971</v>
       </c>
       <c r="B155" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17518,37 +17494,37 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>380941</v>
+        <v>380824</v>
       </c>
       <c r="R155" t="n">
-        <v>6771522</v>
+        <v>6771235</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17575,9 +17551,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17592,22 +17578,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125070222</v>
+        <v>125040199</v>
       </c>
       <c r="B156" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17620,37 +17606,40 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>381053</v>
+        <v>380874</v>
       </c>
       <c r="R156" t="n">
-        <v>6771443</v>
+        <v>6771199</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17677,29 +17666,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -2796,10 +2796,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125070229</v>
+        <v>125041097</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2812,34 +2812,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380971</v>
+        <v>380860</v>
       </c>
       <c r="R21" t="n">
-        <v>6771489</v>
+        <v>6771171</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2869,9 +2869,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2886,22 +2896,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125070236</v>
+        <v>125041868</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2914,34 +2924,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>380922</v>
+        <v>380860</v>
       </c>
       <c r="R22" t="n">
-        <v>6771544</v>
+        <v>6771171</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2971,9 +2981,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2988,22 +3008,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125041868</v>
+        <v>125070229</v>
       </c>
       <c r="B23" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3016,34 +3036,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380860</v>
+        <v>380971</v>
       </c>
       <c r="R23" t="n">
-        <v>6771171</v>
+        <v>6771489</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3073,19 +3093,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3100,22 +3110,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125041097</v>
+        <v>125070236</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3128,34 +3138,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>380860</v>
+        <v>380922</v>
       </c>
       <c r="R24" t="n">
-        <v>6771171</v>
+        <v>6771544</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3185,19 +3195,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3212,19 +3212,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125045234</v>
+        <v>125070219</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3258,22 +3258,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380888</v>
+        <v>381095</v>
       </c>
       <c r="R25" t="n">
-        <v>6771588</v>
+        <v>6771411</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3300,47 +3297,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125046257</v>
+        <v>125070221</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3374,22 +3360,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>381041</v>
+        <v>381059</v>
       </c>
       <c r="R26" t="n">
-        <v>6771405</v>
+        <v>6771421</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3416,50 +3399,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125049925</v>
+        <v>125070247</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3472,40 +3444,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>381316</v>
+        <v>380827</v>
       </c>
       <c r="R27" t="n">
-        <v>6771194</v>
+        <v>6771384</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3532,47 +3501,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125070219</v>
+        <v>125070237</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3612,10 +3570,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>381095</v>
+        <v>380923</v>
       </c>
       <c r="R28" t="n">
-        <v>6771411</v>
+        <v>6771536</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3674,7 +3632,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125070221</v>
+        <v>125070269</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3714,10 +3672,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>381059</v>
+        <v>380938</v>
       </c>
       <c r="R29" t="n">
-        <v>6771421</v>
+        <v>6771234</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3776,10 +3734,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125070247</v>
+        <v>125070201</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3792,21 +3750,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3816,10 +3774,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380827</v>
+        <v>380953</v>
       </c>
       <c r="R30" t="n">
-        <v>6771384</v>
+        <v>6771491</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3878,10 +3836,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125070237</v>
+        <v>125070193</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3894,21 +3852,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3918,10 +3876,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380923</v>
+        <v>380811</v>
       </c>
       <c r="R31" t="n">
-        <v>6771536</v>
+        <v>6771473</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3980,7 +3938,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125070269</v>
+        <v>125045234</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -4014,19 +3972,22 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380938</v>
+        <v>380888</v>
       </c>
       <c r="R32" t="n">
-        <v>6771234</v>
+        <v>6771588</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4053,39 +4014,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125070201</v>
+        <v>125046257</v>
       </c>
       <c r="B33" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4098,37 +4070,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380953</v>
+        <v>381041</v>
       </c>
       <c r="R33" t="n">
-        <v>6771491</v>
+        <v>6771405</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4155,39 +4130,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125070193</v>
+        <v>125049925</v>
       </c>
       <c r="B34" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4200,37 +4186,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380811</v>
+        <v>381316</v>
       </c>
       <c r="R34" t="n">
-        <v>6771473</v>
+        <v>6771194</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4257,29 +4246,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -6176,10 +6176,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125040199</v>
+        <v>125040931</v>
       </c>
       <c r="B52" t="n">
-        <v>78546</v>
+        <v>77738</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6192,21 +6192,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>380874</v>
+        <v>380872</v>
       </c>
       <c r="R52" t="n">
-        <v>6771199</v>
+        <v>6771195</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6292,10 +6292,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125046579</v>
+        <v>125039976</v>
       </c>
       <c r="B53" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6308,21 +6308,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6335,13 +6335,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>381171</v>
+        <v>380856</v>
       </c>
       <c r="R53" t="n">
-        <v>6771315</v>
+        <v>6771167</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6396,22 +6396,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125040931</v>
+        <v>125040199</v>
       </c>
       <c r="B54" t="n">
-        <v>77738</v>
+        <v>78546</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6424,21 +6424,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>380872</v>
+        <v>380874</v>
       </c>
       <c r="R54" t="n">
-        <v>6771195</v>
+        <v>6771199</v>
       </c>
       <c r="S54" t="n">
         <v>9</v>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6524,10 +6524,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125039976</v>
+        <v>125046579</v>
       </c>
       <c r="B55" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6540,21 +6540,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6567,13 +6567,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>380856</v>
+        <v>381171</v>
       </c>
       <c r="R55" t="n">
-        <v>6771167</v>
+        <v>6771315</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6628,12 +6628,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7638,10 +7638,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125070190</v>
+        <v>125046096</v>
       </c>
       <c r="B65" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7654,37 +7654,40 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>381088</v>
+        <v>381038</v>
       </c>
       <c r="R65" t="n">
-        <v>6771369</v>
+        <v>6771446</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7711,36 +7714,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125046096</v>
+        <v>125044939</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7779,17 +7793,17 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>381038</v>
+        <v>380889</v>
       </c>
       <c r="R66" t="n">
-        <v>6771446</v>
+        <v>6771527</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7818,7 +7832,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7828,7 +7842,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7844,19 +7858,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125044939</v>
+        <v>125045848</v>
       </c>
       <c r="B67" t="n">
         <v>78810</v>
@@ -7899,10 +7913,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>380889</v>
+        <v>380967</v>
       </c>
       <c r="R67" t="n">
-        <v>6771527</v>
+        <v>6771519</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7934,7 +7948,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7944,7 +7958,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7965,17 +7979,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125045848</v>
+        <v>125070190</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7988,40 +8002,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>380967</v>
+        <v>381088</v>
       </c>
       <c r="R68" t="n">
-        <v>6771519</v>
+        <v>6771369</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8048,40 +8059,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8408,10 +8408,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125041208</v>
+        <v>125048940</v>
       </c>
       <c r="B72" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8424,34 +8424,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>380840</v>
+        <v>381311</v>
       </c>
       <c r="R72" t="n">
-        <v>6771239</v>
+        <v>6771438</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8483,7 +8486,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8493,7 +8496,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8502,6 +8505,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8513,17 +8517,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125040326</v>
+        <v>125041900</v>
       </c>
       <c r="B73" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8536,37 +8540,40 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>380824</v>
+        <v>380872</v>
       </c>
       <c r="R73" t="n">
-        <v>6771177</v>
+        <v>6771195</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8595,7 +8602,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8605,7 +8612,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8614,28 +8621,29 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125045567</v>
+        <v>125044477</v>
       </c>
       <c r="B74" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8648,21 +8656,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8675,10 +8683,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>380944</v>
+        <v>380848</v>
       </c>
       <c r="R74" t="n">
-        <v>6771491</v>
+        <v>6771395</v>
       </c>
       <c r="S74" t="n">
         <v>8</v>
@@ -8710,7 +8718,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8720,7 +8728,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8748,7 +8756,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125070224</v>
+        <v>125041099</v>
       </c>
       <c r="B75" t="n">
         <v>78810</v>
@@ -8784,17 +8792,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>381027</v>
+        <v>380825</v>
       </c>
       <c r="R75" t="n">
-        <v>6771451</v>
+        <v>6771235</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8821,9 +8829,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8838,19 +8856,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125041099</v>
+        <v>125041252</v>
       </c>
       <c r="B76" t="n">
         <v>78810</v>
@@ -8890,10 +8908,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>380825</v>
+        <v>380848</v>
       </c>
       <c r="R76" t="n">
-        <v>6771235</v>
+        <v>6771237</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8925,7 +8943,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8935,7 +8953,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8962,7 +8980,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125041252</v>
+        <v>125070224</v>
       </c>
       <c r="B77" t="n">
         <v>78810</v>
@@ -8998,17 +9016,17 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>380848</v>
+        <v>381027</v>
       </c>
       <c r="R77" t="n">
-        <v>6771237</v>
+        <v>6771451</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9035,19 +9053,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9062,22 +9070,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125048940</v>
+        <v>125041208</v>
       </c>
       <c r="B78" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9090,37 +9098,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>381311</v>
+        <v>380840</v>
       </c>
       <c r="R78" t="n">
-        <v>6771438</v>
+        <v>6771239</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9152,7 +9157,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9162,7 +9167,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9171,7 +9176,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9183,17 +9187,17 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125041900</v>
+        <v>125040326</v>
       </c>
       <c r="B79" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9206,40 +9210,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>380872</v>
+        <v>380824</v>
       </c>
       <c r="R79" t="n">
-        <v>6771195</v>
+        <v>6771177</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9268,7 +9269,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9278,7 +9279,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9287,29 +9288,28 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125044477</v>
+        <v>125045567</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9322,21 +9322,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9349,10 +9349,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>380848</v>
+        <v>380944</v>
       </c>
       <c r="R80" t="n">
-        <v>6771395</v>
+        <v>6771491</v>
       </c>
       <c r="S80" t="n">
         <v>8</v>
@@ -9384,7 +9384,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9422,10 +9422,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125039727</v>
+        <v>125048909</v>
       </c>
       <c r="B81" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9438,37 +9438,40 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Vålviken, Vålviken, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>380927</v>
+        <v>381320</v>
       </c>
       <c r="R81" t="n">
-        <v>6771248</v>
+        <v>6771437</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9497,7 +9500,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9507,7 +9510,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9516,25 +9519,26 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125045862</v>
+        <v>125044489</v>
       </c>
       <c r="B82" t="n">
         <v>78810</v>
@@ -9573,17 +9577,17 @@
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>380944</v>
+        <v>380835</v>
       </c>
       <c r="R82" t="n">
-        <v>6771491</v>
+        <v>6771422</v>
       </c>
       <c r="S82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9612,7 +9616,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9622,7 +9626,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9638,19 +9642,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125048909</v>
+        <v>125040000</v>
       </c>
       <c r="B83" t="n">
         <v>78810</v>
@@ -9684,22 +9688,19 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>381320</v>
+        <v>380848</v>
       </c>
       <c r="R83" t="n">
-        <v>6771437</v>
+        <v>6771174</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9728,7 +9729,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9738,7 +9739,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9747,7 +9748,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9759,17 +9759,17 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125044489</v>
+        <v>125039727</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9782,40 +9782,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Vålviken, Vålviken, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>380835</v>
+        <v>380927</v>
       </c>
       <c r="R84" t="n">
-        <v>6771422</v>
+        <v>6771248</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9844,7 +9841,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9854,7 +9851,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9863,26 +9860,25 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125040000</v>
+        <v>125045862</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9916,19 +9912,22 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>380848</v>
+        <v>380944</v>
       </c>
       <c r="R85" t="n">
-        <v>6771174</v>
+        <v>6771491</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9957,7 +9956,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9967,7 +9966,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9976,18 +9975,19 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10954,10 +10954,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125039570</v>
+        <v>125045458</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10970,37 +10970,40 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>380934</v>
+        <v>380944</v>
       </c>
       <c r="R95" t="n">
-        <v>6771147</v>
+        <v>6771491</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11029,7 +11032,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11039,7 +11042,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11048,28 +11051,29 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125049054</v>
+        <v>125045155</v>
       </c>
       <c r="B96" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11082,21 +11086,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11105,17 +11109,17 @@
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>381309</v>
+        <v>380803</v>
       </c>
       <c r="R96" t="n">
-        <v>6771459</v>
+        <v>6771421</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11144,7 +11148,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11154,7 +11158,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11170,22 +11174,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125045458</v>
+        <v>125039570</v>
       </c>
       <c r="B97" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11198,40 +11202,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>380944</v>
+        <v>380934</v>
       </c>
       <c r="R97" t="n">
-        <v>6771491</v>
+        <v>6771147</v>
       </c>
       <c r="S97" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11260,7 +11261,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11270,7 +11271,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11279,29 +11280,28 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125045155</v>
+        <v>125070205</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11314,40 +11314,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>380803</v>
+        <v>380806</v>
       </c>
       <c r="R98" t="n">
-        <v>6771421</v>
+        <v>6771391</v>
       </c>
       <c r="S98" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11374,50 +11371,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125070205</v>
+        <v>125070253</v>
       </c>
       <c r="B99" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11430,21 +11416,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11454,10 +11440,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>380806</v>
+        <v>380966</v>
       </c>
       <c r="R99" t="n">
-        <v>6771391</v>
+        <v>6771241</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11516,7 +11502,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125070253</v>
+        <v>125070258</v>
       </c>
       <c r="B100" t="n">
         <v>78810</v>
@@ -11556,10 +11542,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>380966</v>
+        <v>380783</v>
       </c>
       <c r="R100" t="n">
-        <v>6771241</v>
+        <v>6771123</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -11618,7 +11604,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125070258</v>
+        <v>125070260</v>
       </c>
       <c r="B101" t="n">
         <v>78810</v>
@@ -11658,10 +11644,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>380783</v>
+        <v>380775</v>
       </c>
       <c r="R101" t="n">
-        <v>6771123</v>
+        <v>6771061</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11720,10 +11706,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125070260</v>
+        <v>125049054</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11736,37 +11722,40 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>380775</v>
+        <v>381309</v>
       </c>
       <c r="R102" t="n">
-        <v>6771061</v>
+        <v>6771459</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11793,29 +11782,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -14402,10 +14402,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125049508</v>
+        <v>125041650</v>
       </c>
       <c r="B127" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14418,37 +14418,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>381324</v>
+        <v>380874</v>
       </c>
       <c r="R127" t="n">
-        <v>6771331</v>
+        <v>6771241</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14480,7 +14477,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14490,7 +14487,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14499,7 +14496,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14518,7 +14514,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125044547</v>
+        <v>125042305</v>
       </c>
       <c r="B128" t="n">
         <v>78810</v>
@@ -14557,17 +14553,17 @@
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>380821</v>
+        <v>380940</v>
       </c>
       <c r="R128" t="n">
-        <v>6771374</v>
+        <v>6771238</v>
       </c>
       <c r="S128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14596,7 +14592,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14606,7 +14602,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14622,19 +14618,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125049533</v>
+        <v>125049508</v>
       </c>
       <c r="B129" t="n">
         <v>78546</v>
@@ -14673,17 +14669,17 @@
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>381300</v>
+        <v>381324</v>
       </c>
       <c r="R129" t="n">
-        <v>6771367</v>
+        <v>6771331</v>
       </c>
       <c r="S129" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14712,7 +14708,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14722,7 +14718,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14738,19 +14734,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125041650</v>
+        <v>125044547</v>
       </c>
       <c r="B130" t="n">
         <v>78810</v>
@@ -14784,19 +14780,22 @@
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>380874</v>
+        <v>380821</v>
       </c>
       <c r="R130" t="n">
-        <v>6771241</v>
+        <v>6771374</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14825,7 +14824,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14835,7 +14834,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14844,28 +14843,29 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125042305</v>
+        <v>125049533</v>
       </c>
       <c r="B131" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14878,21 +14878,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14901,17 +14901,17 @@
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>380940</v>
+        <v>381300</v>
       </c>
       <c r="R131" t="n">
-        <v>6771238</v>
+        <v>6771367</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14966,12 +14966,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
@@ -15498,10 +15498,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125070220</v>
+        <v>125070200</v>
       </c>
       <c r="B137" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15514,21 +15514,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>381096</v>
+        <v>380812</v>
       </c>
       <c r="R137" t="n">
-        <v>6771419</v>
+        <v>6771391</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15600,10 +15600,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125070231</v>
+        <v>125070199</v>
       </c>
       <c r="B138" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15616,21 +15616,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15640,10 +15640,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>380946</v>
+        <v>380948</v>
       </c>
       <c r="R138" t="n">
-        <v>6771491</v>
+        <v>6771512</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15702,10 +15702,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125070259</v>
+        <v>125039513</v>
       </c>
       <c r="B139" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15718,34 +15718,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>380780</v>
+        <v>380934</v>
       </c>
       <c r="R139" t="n">
-        <v>6771075</v>
+        <v>6771147</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15775,9 +15775,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15804,10 +15814,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125070250</v>
+        <v>125042523</v>
       </c>
       <c r="B140" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15820,37 +15830,40 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>380990</v>
+        <v>381014</v>
       </c>
       <c r="R140" t="n">
-        <v>6771182</v>
+        <v>6771206</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15877,36 +15890,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125039513</v>
+        <v>125046556</v>
       </c>
       <c r="B141" t="n">
         <v>78547</v>
@@ -15940,19 +15964,22 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>380934</v>
+        <v>381175</v>
       </c>
       <c r="R141" t="n">
-        <v>6771147</v>
+        <v>6771338</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15981,7 +16008,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15991,7 +16018,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16000,28 +16027,29 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125042523</v>
+        <v>125070220</v>
       </c>
       <c r="B142" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -16034,40 +16062,37 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>381014</v>
+        <v>381096</v>
       </c>
       <c r="R142" t="n">
-        <v>6771206</v>
+        <v>6771419</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16094,50 +16119,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125046556</v>
+        <v>125070231</v>
       </c>
       <c r="B143" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -16150,40 +16164,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>381175</v>
+        <v>380946</v>
       </c>
       <c r="R143" t="n">
-        <v>6771338</v>
+        <v>6771491</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16210,50 +16221,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:24</t>
-        </is>
-      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125070200</v>
+        <v>125070259</v>
       </c>
       <c r="B144" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16266,21 +16266,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16290,10 +16290,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>380812</v>
+        <v>380780</v>
       </c>
       <c r="R144" t="n">
-        <v>6771391</v>
+        <v>6771075</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16352,10 +16352,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125070199</v>
+        <v>125070250</v>
       </c>
       <c r="B145" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -16368,21 +16368,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16392,10 +16392,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>380948</v>
+        <v>380990</v>
       </c>
       <c r="R145" t="n">
-        <v>6771512</v>
+        <v>6771182</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16454,10 +16454,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125041901</v>
+        <v>125070191</v>
       </c>
       <c r="B146" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16470,37 +16470,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>380904</v>
+        <v>380812</v>
       </c>
       <c r="R146" t="n">
-        <v>6771257</v>
+        <v>6771477</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16527,19 +16527,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>12:37</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16554,19 +16544,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125070202</v>
+        <v>125041901</v>
       </c>
       <c r="B147" t="n">
         <v>78546</v>
@@ -16602,17 +16592,17 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>381352</v>
+        <v>380904</v>
       </c>
       <c r="R147" t="n">
-        <v>6771302</v>
+        <v>6771257</v>
       </c>
       <c r="S147" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16639,9 +16629,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16656,19 +16656,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125050619</v>
+        <v>125070202</v>
       </c>
       <c r="B148" t="n">
         <v>78546</v>
@@ -16702,19 +16702,16 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>381293</v>
+        <v>381352</v>
       </c>
       <c r="R148" t="n">
-        <v>6770938</v>
+        <v>6771302</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -16744,50 +16741,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125070254</v>
+        <v>125050619</v>
       </c>
       <c r="B149" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16800,34 +16786,37 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>380901</v>
+        <v>381293</v>
       </c>
       <c r="R149" t="n">
-        <v>6771241</v>
+        <v>6770938</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -16857,39 +16846,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125070191</v>
+        <v>125070254</v>
       </c>
       <c r="B150" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16902,21 +16902,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16926,10 +16926,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>380812</v>
+        <v>380901</v>
       </c>
       <c r="R150" t="n">
-        <v>6771477</v>
+        <v>6771241</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -16988,10 +16988,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125044507</v>
+        <v>125040971</v>
       </c>
       <c r="B151" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -17004,37 +17004,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>380829</v>
+        <v>380824</v>
       </c>
       <c r="R151" t="n">
-        <v>6771431</v>
+        <v>6771235</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17066,7 +17063,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17076,7 +17073,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17085,7 +17082,6 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -17097,14 +17093,14 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125045538</v>
+        <v>125044507</v>
       </c>
       <c r="B152" t="n">
         <v>78810</v>
@@ -17147,10 +17143,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>380927</v>
+        <v>380829</v>
       </c>
       <c r="R152" t="n">
-        <v>6771538</v>
+        <v>6771431</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17182,7 +17178,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17192,7 +17188,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17213,14 +17209,14 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125070208</v>
+        <v>125045538</v>
       </c>
       <c r="B153" t="n">
         <v>78810</v>
@@ -17254,19 +17250,22 @@
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>381532</v>
+        <v>380927</v>
       </c>
       <c r="R153" t="n">
-        <v>6771209</v>
+        <v>6771538</v>
       </c>
       <c r="S153" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17293,39 +17292,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
       <c r="AD153" t="b">
         <v>0</v>
       </c>
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125070210</v>
+        <v>125040613</v>
       </c>
       <c r="B154" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -17338,34 +17348,34 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>381370</v>
+        <v>380860</v>
       </c>
       <c r="R154" t="n">
-        <v>6771255</v>
+        <v>6771171</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -17395,9 +17405,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17412,19 +17432,19 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125070214</v>
+        <v>125048937</v>
       </c>
       <c r="B155" t="n">
         <v>78810</v>
@@ -17458,19 +17478,22 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>381359</v>
+        <v>381300</v>
       </c>
       <c r="R155" t="n">
-        <v>6771390</v>
+        <v>6771367</v>
       </c>
       <c r="S155" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17497,36 +17520,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125070235</v>
+        <v>125070208</v>
       </c>
       <c r="B156" t="n">
         <v>78810</v>
@@ -17566,10 +17600,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>380941</v>
+        <v>381532</v>
       </c>
       <c r="R156" t="n">
-        <v>6771522</v>
+        <v>6771209</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -17628,7 +17662,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125070266</v>
+        <v>125070210</v>
       </c>
       <c r="B157" t="n">
         <v>78810</v>
@@ -17668,10 +17702,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>380889</v>
+        <v>381370</v>
       </c>
       <c r="R157" t="n">
-        <v>6771552</v>
+        <v>6771255</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17730,10 +17764,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125040613</v>
+        <v>125070214</v>
       </c>
       <c r="B158" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17746,34 +17780,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>380860</v>
+        <v>381359</v>
       </c>
       <c r="R158" t="n">
-        <v>6771171</v>
+        <v>6771390</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -17803,19 +17837,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17830,22 +17854,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125040971</v>
+        <v>125070235</v>
       </c>
       <c r="B159" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17858,37 +17882,37 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>380824</v>
+        <v>380941</v>
       </c>
       <c r="R159" t="n">
-        <v>6771235</v>
+        <v>6771522</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17915,19 +17939,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17942,19 +17956,19 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125048937</v>
+        <v>125070266</v>
       </c>
       <c r="B160" t="n">
         <v>78810</v>
@@ -17988,22 +18002,19 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>381300</v>
+        <v>380889</v>
       </c>
       <c r="R160" t="n">
-        <v>6771367</v>
+        <v>6771552</v>
       </c>
       <c r="S160" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18030,40 +18041,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>16:18</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -18622,10 +18622,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125044481</v>
+        <v>125044862</v>
       </c>
       <c r="B166" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18638,21 +18638,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18661,17 +18661,17 @@
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>380836</v>
+        <v>380803</v>
       </c>
       <c r="R166" t="n">
-        <v>6771422</v>
+        <v>6771421</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18710,7 +18710,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18726,19 +18726,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125040302</v>
+        <v>125044481</v>
       </c>
       <c r="B167" t="n">
         <v>78810</v>
@@ -18772,16 +18772,19 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380817</v>
+        <v>380836</v>
       </c>
       <c r="R167" t="n">
-        <v>6771175</v>
+        <v>6771422</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18813,7 +18816,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18823,7 +18826,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18832,6 +18835,7 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
@@ -18843,17 +18847,17 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125044862</v>
+        <v>125040302</v>
       </c>
       <c r="B168" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18866,40 +18870,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380803</v>
+        <v>380817</v>
       </c>
       <c r="R168" t="n">
-        <v>6771421</v>
+        <v>6771175</v>
       </c>
       <c r="S168" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -18928,7 +18929,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18938,7 +18939,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18947,19 +18948,18 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -3460,10 +3460,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125070229</v>
+        <v>125044337</v>
       </c>
       <c r="B27" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3476,34 +3476,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380971</v>
+        <v>380860</v>
       </c>
       <c r="R27" t="n">
-        <v>6771489</v>
+        <v>6771171</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3533,9 +3533,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3550,12 +3560,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3678,10 +3688,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125045567</v>
+        <v>125070229</v>
       </c>
       <c r="B29" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3694,40 +3704,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380944</v>
+        <v>380971</v>
       </c>
       <c r="R29" t="n">
-        <v>6771491</v>
+        <v>6771489</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3754,47 +3761,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125040653</v>
+        <v>125045567</v>
       </c>
       <c r="B30" t="n">
         <v>78684</v>
@@ -3833,14 +3829,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380872</v>
+        <v>380944</v>
       </c>
       <c r="R30" t="n">
-        <v>6771195</v>
+        <v>6771491</v>
       </c>
       <c r="S30" t="n">
         <v>8</v>
@@ -3872,7 +3868,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3882,7 +3878,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3910,7 +3906,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125049054</v>
+        <v>125040653</v>
       </c>
       <c r="B31" t="n">
         <v>78684</v>
@@ -3953,13 +3949,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>381309</v>
+        <v>380872</v>
       </c>
       <c r="R31" t="n">
-        <v>6771459</v>
+        <v>6771195</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3988,7 +3984,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3998,7 +3994,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,19 +4010,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125048854</v>
+        <v>125049054</v>
       </c>
       <c r="B32" t="n">
         <v>78684</v>
@@ -4065,17 +4061,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>381300</v>
+        <v>381309</v>
       </c>
       <c r="R32" t="n">
-        <v>6771367</v>
+        <v>6771459</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4104,7 +4100,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4114,7 +4110,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4130,19 +4126,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125041603</v>
+        <v>125048854</v>
       </c>
       <c r="B33" t="n">
         <v>78684</v>
@@ -4176,19 +4172,22 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380860</v>
+        <v>381300</v>
       </c>
       <c r="R33" t="n">
-        <v>6771171</v>
+        <v>6771367</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4217,7 +4216,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4227,7 +4226,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4236,18 +4235,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -6658,7 +6658,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125070215</v>
+        <v>125070210</v>
       </c>
       <c r="B56" t="n">
         <v>78947</v>
@@ -6698,10 +6698,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>381346</v>
+        <v>381370</v>
       </c>
       <c r="R56" t="n">
-        <v>6771363</v>
+        <v>6771255</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6760,7 +6760,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125070260</v>
+        <v>125070215</v>
       </c>
       <c r="B57" t="n">
         <v>78947</v>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>380775</v>
+        <v>381346</v>
       </c>
       <c r="R57" t="n">
-        <v>6771061</v>
+        <v>6771363</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125070210</v>
+        <v>125070260</v>
       </c>
       <c r="B61" t="n">
         <v>78947</v>
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>381370</v>
+        <v>380775</v>
       </c>
       <c r="R61" t="n">
-        <v>6771255</v>
+        <v>6771061</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7308,7 +7308,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125070244</v>
+        <v>125040890</v>
       </c>
       <c r="B62" t="n">
         <v>78947</v>
@@ -7344,17 +7344,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>380850</v>
+        <v>380824</v>
       </c>
       <c r="R62" t="n">
-        <v>6771542</v>
+        <v>6771234</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7381,9 +7381,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7398,19 +7408,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125070258</v>
+        <v>125044507</v>
       </c>
       <c r="B63" t="n">
         <v>78947</v>
@@ -7444,19 +7454,22 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>380783</v>
+        <v>380829</v>
       </c>
       <c r="R63" t="n">
-        <v>6771123</v>
+        <v>6771431</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7483,36 +7496,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125041252</v>
+        <v>125046096</v>
       </c>
       <c r="B64" t="n">
         <v>78947</v>
@@ -7546,19 +7570,22 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>380848</v>
+        <v>381038</v>
       </c>
       <c r="R64" t="n">
-        <v>6771237</v>
+        <v>6771446</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7587,7 +7614,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7597,7 +7624,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7606,28 +7633,29 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125040104</v>
+        <v>125045862</v>
       </c>
       <c r="B65" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7640,37 +7668,40 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>380842</v>
+        <v>380944</v>
       </c>
       <c r="R65" t="n">
-        <v>6771175</v>
+        <v>6771491</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7699,7 +7730,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7709,7 +7740,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7718,25 +7749,26 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125040890</v>
+        <v>125070244</v>
       </c>
       <c r="B66" t="n">
         <v>78947</v>
@@ -7772,17 +7804,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>380824</v>
+        <v>380850</v>
       </c>
       <c r="R66" t="n">
-        <v>6771234</v>
+        <v>6771542</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7809,19 +7841,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7836,19 +7858,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125044507</v>
+        <v>125070258</v>
       </c>
       <c r="B67" t="n">
         <v>78947</v>
@@ -7882,22 +7904,19 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>380829</v>
+        <v>380783</v>
       </c>
       <c r="R67" t="n">
-        <v>6771431</v>
+        <v>6771123</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7924,50 +7943,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125046096</v>
+        <v>125046270</v>
       </c>
       <c r="B68" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7980,21 +7988,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8003,17 +8011,17 @@
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>381038</v>
+        <v>381095</v>
       </c>
       <c r="R68" t="n">
-        <v>6771446</v>
+        <v>6771385</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8042,7 +8050,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8052,7 +8060,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8068,22 +8076,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125045862</v>
+        <v>125049925</v>
       </c>
       <c r="B69" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8096,21 +8104,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8123,13 +8131,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>380944</v>
+        <v>381316</v>
       </c>
       <c r="R69" t="n">
-        <v>6771491</v>
+        <v>6771194</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8158,7 +8166,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8168,7 +8176,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8196,10 +8204,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125046270</v>
+        <v>125041252</v>
       </c>
       <c r="B70" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8212,37 +8220,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>381095</v>
+        <v>380848</v>
       </c>
       <c r="R70" t="n">
-        <v>6771385</v>
+        <v>6771237</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8274,7 +8279,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8284,7 +8289,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8293,7 +8298,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8305,17 +8309,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125049925</v>
+        <v>125040104</v>
       </c>
       <c r="B71" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8328,37 +8332,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>381316</v>
+        <v>380842</v>
       </c>
       <c r="R71" t="n">
-        <v>6771194</v>
+        <v>6771175</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8390,7 +8391,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8400,7 +8401,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8409,19 +8410,18 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -13111,10 +13111,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125070200</v>
+        <v>125049428</v>
       </c>
       <c r="B115" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13127,37 +13127,40 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>380812</v>
+        <v>381345</v>
       </c>
       <c r="R115" t="n">
-        <v>6771391</v>
+        <v>6771402</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13184,39 +13187,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125070271</v>
+        <v>125040199</v>
       </c>
       <c r="B116" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13229,37 +13243,40 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>380767</v>
+        <v>380874</v>
       </c>
       <c r="R116" t="n">
-        <v>6770999</v>
+        <v>6771199</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13286,36 +13303,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125070204</v>
+        <v>125070202</v>
       </c>
       <c r="B117" t="n">
         <v>78683</v>
@@ -13355,10 +13383,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>381311</v>
+        <v>381352</v>
       </c>
       <c r="R117" t="n">
-        <v>6771370</v>
+        <v>6771302</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13417,7 +13445,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125070211</v>
+        <v>125070218</v>
       </c>
       <c r="B118" t="n">
         <v>78947</v>
@@ -13457,10 +13485,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>381359</v>
+        <v>381266</v>
       </c>
       <c r="R118" t="n">
-        <v>6771263</v>
+        <v>6771351</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13519,10 +13547,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125070202</v>
+        <v>125070271</v>
       </c>
       <c r="B119" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13535,21 +13563,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13559,10 +13587,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>381352</v>
+        <v>380767</v>
       </c>
       <c r="R119" t="n">
-        <v>6771302</v>
+        <v>6770999</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13621,10 +13649,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125070218</v>
+        <v>125070204</v>
       </c>
       <c r="B120" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13637,21 +13665,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13661,10 +13689,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>381266</v>
+        <v>381311</v>
       </c>
       <c r="R120" t="n">
-        <v>6771351</v>
+        <v>6771370</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13723,10 +13751,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125042523</v>
+        <v>125070211</v>
       </c>
       <c r="B121" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13739,40 +13767,37 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>381014</v>
+        <v>381359</v>
       </c>
       <c r="R121" t="n">
-        <v>6771206</v>
+        <v>6771263</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13799,50 +13824,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125044862</v>
+        <v>125042523</v>
       </c>
       <c r="B122" t="n">
-        <v>79536</v>
+        <v>78684</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13855,21 +13869,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13878,17 +13892,17 @@
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>380803</v>
+        <v>381014</v>
       </c>
       <c r="R122" t="n">
-        <v>6771421</v>
+        <v>6771206</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13917,7 +13931,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13927,7 +13941,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13943,22 +13957,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125049428</v>
+        <v>125044862</v>
       </c>
       <c r="B123" t="n">
-        <v>78947</v>
+        <v>79536</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13971,21 +13985,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13994,17 +14008,17 @@
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>381345</v>
+        <v>380803</v>
       </c>
       <c r="R123" t="n">
-        <v>6771402</v>
+        <v>6771421</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -14033,7 +14047,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14043,7 +14057,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14059,22 +14073,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125040199</v>
+        <v>125070200</v>
       </c>
       <c r="B124" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14087,40 +14101,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>380874</v>
+        <v>380812</v>
       </c>
       <c r="R124" t="n">
-        <v>6771199</v>
+        <v>6771391</v>
       </c>
       <c r="S124" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14147,40 +14158,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -16272,10 +16272,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125040613</v>
+        <v>125070221</v>
       </c>
       <c r="B144" t="n">
-        <v>79536</v>
+        <v>78947</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -16288,34 +16288,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>380860</v>
+        <v>381059</v>
       </c>
       <c r="R144" t="n">
-        <v>6771171</v>
+        <v>6771421</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -16345,19 +16345,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16372,19 +16362,19 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125070221</v>
+        <v>125070253</v>
       </c>
       <c r="B145" t="n">
         <v>78947</v>
@@ -16424,10 +16414,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>381059</v>
+        <v>380966</v>
       </c>
       <c r="R145" t="n">
-        <v>6771421</v>
+        <v>6771241</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -16486,10 +16476,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125070253</v>
+        <v>125040613</v>
       </c>
       <c r="B146" t="n">
-        <v>78947</v>
+        <v>79536</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16502,34 +16492,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>380966</v>
+        <v>380860</v>
       </c>
       <c r="R146" t="n">
-        <v>6771241</v>
+        <v>6771171</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -16559,9 +16549,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16576,12 +16576,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -18000,7 +18000,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125070268</v>
+        <v>125070270</v>
       </c>
       <c r="B160" t="n">
         <v>78947</v>
@@ -18040,10 +18040,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>380854</v>
+        <v>380826</v>
       </c>
       <c r="R160" t="n">
-        <v>6771477</v>
+        <v>6771195</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -18102,7 +18102,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125070270</v>
+        <v>125070235</v>
       </c>
       <c r="B161" t="n">
         <v>78947</v>
@@ -18142,10 +18142,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>380826</v>
+        <v>380941</v>
       </c>
       <c r="R161" t="n">
-        <v>6771195</v>
+        <v>6771522</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -18204,7 +18204,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125070235</v>
+        <v>125070238</v>
       </c>
       <c r="B162" t="n">
         <v>78947</v>
@@ -18244,10 +18244,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>380941</v>
+        <v>380917</v>
       </c>
       <c r="R162" t="n">
-        <v>6771522</v>
+        <v>6771547</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18306,7 +18306,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125070238</v>
+        <v>125070268</v>
       </c>
       <c r="B163" t="n">
         <v>78947</v>
@@ -18346,10 +18346,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>380917</v>
+        <v>380854</v>
       </c>
       <c r="R163" t="n">
-        <v>6771547</v>
+        <v>6771477</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18756,10 +18756,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125070232</v>
+        <v>125041141</v>
       </c>
       <c r="B167" t="n">
-        <v>78947</v>
+        <v>79565</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18772,37 +18772,37 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380944</v>
+        <v>380828</v>
       </c>
       <c r="R167" t="n">
-        <v>6771499</v>
+        <v>6771239</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18829,9 +18829,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18846,22 +18856,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125041141</v>
+        <v>125045211</v>
       </c>
       <c r="B168" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18874,34 +18884,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>380828</v>
+        <v>380887</v>
       </c>
       <c r="R168" t="n">
-        <v>6771239</v>
+        <v>6771583</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18933,7 +18946,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18943,7 +18956,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18952,6 +18965,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -18963,14 +18977,14 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125045211</v>
+        <v>125044489</v>
       </c>
       <c r="B169" t="n">
         <v>78947</v>
@@ -19013,10 +19027,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>380887</v>
+        <v>380835</v>
       </c>
       <c r="R169" t="n">
-        <v>6771583</v>
+        <v>6771422</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19048,7 +19062,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19058,7 +19072,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19086,7 +19100,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125044489</v>
+        <v>125040000</v>
       </c>
       <c r="B170" t="n">
         <v>78947</v>
@@ -19120,22 +19134,19 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>380835</v>
+        <v>380848</v>
       </c>
       <c r="R170" t="n">
-        <v>6771422</v>
+        <v>6771174</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -19164,7 +19175,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19174,7 +19185,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19183,7 +19194,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -19195,14 +19205,14 @@
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125040000</v>
+        <v>125070232</v>
       </c>
       <c r="B171" t="n">
         <v>78947</v>
@@ -19238,14 +19248,14 @@
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>380848</v>
+        <v>380944</v>
       </c>
       <c r="R171" t="n">
-        <v>6771174</v>
+        <v>6771499</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -19275,19 +19285,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>11:29</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19302,12 +19302,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -7017,10 +7017,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125050542</v>
+        <v>125070211</v>
       </c>
       <c r="B59" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7033,40 +7033,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>381332</v>
+        <v>381359</v>
       </c>
       <c r="R59" t="n">
-        <v>6770903</v>
+        <v>6771263</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7093,50 +7090,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125041757</v>
+        <v>125050284</v>
       </c>
       <c r="B60" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7149,37 +7135,40 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>380887</v>
+        <v>381346</v>
       </c>
       <c r="R60" t="n">
-        <v>6771232</v>
+        <v>6771055</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7208,7 +7197,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7218,7 +7207,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7227,6 +7216,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7238,14 +7228,14 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125070211</v>
+        <v>125041757</v>
       </c>
       <c r="B61" t="n">
         <v>78947</v>
@@ -7281,17 +7271,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>381359</v>
+        <v>380887</v>
       </c>
       <c r="R61" t="n">
-        <v>6771263</v>
+        <v>6771232</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7318,9 +7308,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7335,22 +7335,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125050284</v>
+        <v>125050542</v>
       </c>
       <c r="B62" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7363,21 +7363,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7390,13 +7390,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>381346</v>
+        <v>381332</v>
       </c>
       <c r="R62" t="n">
-        <v>6771055</v>
+        <v>6770903</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7463,10 +7463,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125070252</v>
+        <v>125047288</v>
       </c>
       <c r="B63" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7479,37 +7479,40 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>380991</v>
+        <v>381041</v>
       </c>
       <c r="R63" t="n">
-        <v>6771255</v>
+        <v>6771405</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7536,36 +7539,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125070235</v>
+        <v>125070269</v>
       </c>
       <c r="B64" t="n">
         <v>78947</v>
@@ -7605,10 +7619,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>380941</v>
+        <v>380938</v>
       </c>
       <c r="R64" t="n">
-        <v>6771522</v>
+        <v>6771234</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7667,7 +7681,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125070232</v>
+        <v>125044489</v>
       </c>
       <c r="B65" t="n">
         <v>78947</v>
@@ -7701,19 +7715,22 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>380944</v>
+        <v>380835</v>
       </c>
       <c r="R65" t="n">
-        <v>6771499</v>
+        <v>6771422</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7740,36 +7757,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125070248</v>
+        <v>125044246</v>
       </c>
       <c r="B66" t="n">
         <v>78947</v>
@@ -7803,16 +7831,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>380858</v>
+        <v>380900</v>
       </c>
       <c r="R66" t="n">
-        <v>6771400</v>
+        <v>6771401</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7842,36 +7873,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125070269</v>
+        <v>125070252</v>
       </c>
       <c r="B67" t="n">
         <v>78947</v>
@@ -7911,10 +7953,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>380938</v>
+        <v>380991</v>
       </c>
       <c r="R67" t="n">
-        <v>6771234</v>
+        <v>6771255</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7973,7 +8015,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125070254</v>
+        <v>125070235</v>
       </c>
       <c r="B68" t="n">
         <v>78947</v>
@@ -8013,10 +8055,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>380901</v>
+        <v>380941</v>
       </c>
       <c r="R68" t="n">
-        <v>6771241</v>
+        <v>6771522</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8075,7 +8117,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125044489</v>
+        <v>125070232</v>
       </c>
       <c r="B69" t="n">
         <v>78947</v>
@@ -8109,22 +8151,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>380835</v>
+        <v>380944</v>
       </c>
       <c r="R69" t="n">
-        <v>6771422</v>
+        <v>6771499</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8151,47 +8190,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125044246</v>
+        <v>125070248</v>
       </c>
       <c r="B70" t="n">
         <v>78947</v>
@@ -8225,19 +8253,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>380900</v>
+        <v>380858</v>
       </c>
       <c r="R70" t="n">
-        <v>6771401</v>
+        <v>6771400</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8267,50 +8292,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125047288</v>
+        <v>125070254</v>
       </c>
       <c r="B71" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8323,40 +8337,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>381041</v>
+        <v>380901</v>
       </c>
       <c r="R71" t="n">
-        <v>6771405</v>
+        <v>6771241</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8383,40 +8394,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9505,7 +9505,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125070214</v>
+        <v>125039429</v>
       </c>
       <c r="B82" t="n">
         <v>78947</v>
@@ -9541,14 +9541,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>381359</v>
+        <v>380933</v>
       </c>
       <c r="R82" t="n">
-        <v>6771390</v>
+        <v>6771152</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9578,9 +9578,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9607,10 +9617,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125070234</v>
+        <v>125040104</v>
       </c>
       <c r="B83" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9623,37 +9633,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>380940</v>
+        <v>380842</v>
       </c>
       <c r="R83" t="n">
-        <v>6771511</v>
+        <v>6771175</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9680,9 +9690,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9697,22 +9717,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125070205</v>
+        <v>125045567</v>
       </c>
       <c r="B84" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9725,37 +9745,40 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>380806</v>
+        <v>380944</v>
       </c>
       <c r="R84" t="n">
-        <v>6771391</v>
+        <v>6771491</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9782,36 +9805,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125045567</v>
+        <v>125044233</v>
       </c>
       <c r="B85" t="n">
         <v>78684</v>
@@ -9850,17 +9884,17 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>380944</v>
+        <v>380900</v>
       </c>
       <c r="R85" t="n">
-        <v>6771491</v>
+        <v>6771401</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9889,7 +9923,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9899,7 +9933,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9915,22 +9949,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125044233</v>
+        <v>125046257</v>
       </c>
       <c r="B86" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9943,21 +9977,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9966,17 +10000,17 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>380900</v>
+        <v>381041</v>
       </c>
       <c r="R86" t="n">
-        <v>6771401</v>
+        <v>6771405</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10005,7 +10039,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10015,7 +10049,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10031,19 +10065,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125039429</v>
+        <v>125046145</v>
       </c>
       <c r="B87" t="n">
         <v>78947</v>
@@ -10077,16 +10111,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>380933</v>
+        <v>381076</v>
       </c>
       <c r="R87" t="n">
-        <v>6771152</v>
+        <v>6771400</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -10118,7 +10155,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10128,7 +10165,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10137,28 +10174,29 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125040104</v>
+        <v>125070214</v>
       </c>
       <c r="B88" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10171,37 +10209,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>380842</v>
+        <v>381359</v>
       </c>
       <c r="R88" t="n">
-        <v>6771175</v>
+        <v>6771390</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10228,19 +10266,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:34</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10255,19 +10283,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125046257</v>
+        <v>125070234</v>
       </c>
       <c r="B89" t="n">
         <v>78947</v>
@@ -10301,22 +10329,19 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>381041</v>
+        <v>380940</v>
       </c>
       <c r="R89" t="n">
-        <v>6771405</v>
+        <v>6771511</v>
       </c>
       <c r="S89" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10343,50 +10368,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125046145</v>
+        <v>125070205</v>
       </c>
       <c r="B90" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10399,37 +10413,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>381076</v>
+        <v>380806</v>
       </c>
       <c r="R90" t="n">
-        <v>6771400</v>
+        <v>6771391</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -10459,40 +10470,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11153,7 +11153,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125070207</v>
+        <v>125046096</v>
       </c>
       <c r="B97" t="n">
         <v>78947</v>
@@ -11187,19 +11187,22 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>381296</v>
+        <v>381038</v>
       </c>
       <c r="R97" t="n">
-        <v>6771103</v>
+        <v>6771446</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11226,36 +11229,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125070243</v>
+        <v>125045155</v>
       </c>
       <c r="B98" t="n">
         <v>78947</v>
@@ -11289,19 +11303,22 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>380887</v>
+        <v>380803</v>
       </c>
       <c r="R98" t="n">
-        <v>6771552</v>
+        <v>6771421</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11328,36 +11345,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125070247</v>
+        <v>125070207</v>
       </c>
       <c r="B99" t="n">
         <v>78947</v>
@@ -11397,10 +11425,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>380827</v>
+        <v>381296</v>
       </c>
       <c r="R99" t="n">
-        <v>6771384</v>
+        <v>6771103</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11459,10 +11487,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125049508</v>
+        <v>125070243</v>
       </c>
       <c r="B100" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11475,40 +11503,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>381324</v>
+        <v>380887</v>
       </c>
       <c r="R100" t="n">
-        <v>6771331</v>
+        <v>6771552</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11535,47 +11560,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125046096</v>
+        <v>125070247</v>
       </c>
       <c r="B101" t="n">
         <v>78947</v>
@@ -11609,22 +11623,19 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>381038</v>
+        <v>380827</v>
       </c>
       <c r="R101" t="n">
-        <v>6771446</v>
+        <v>6771384</v>
       </c>
       <c r="S101" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11651,50 +11662,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>15:06</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125045155</v>
+        <v>125049508</v>
       </c>
       <c r="B102" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11707,21 +11707,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11730,17 +11730,17 @@
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>380803</v>
+        <v>381324</v>
       </c>
       <c r="R102" t="n">
-        <v>6771421</v>
+        <v>6771331</v>
       </c>
       <c r="S102" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11795,12 +11795,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -13233,10 +13233,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125050455</v>
+        <v>125044507</v>
       </c>
       <c r="B116" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13249,21 +13249,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13276,10 +13276,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>381361</v>
+        <v>380829</v>
       </c>
       <c r="R116" t="n">
-        <v>6770935</v>
+        <v>6771431</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13311,7 +13311,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13342,14 +13342,14 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125044507</v>
+        <v>125040000</v>
       </c>
       <c r="B117" t="n">
         <v>78947</v>
@@ -13383,22 +13383,19 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>380829</v>
+        <v>380848</v>
       </c>
       <c r="R117" t="n">
-        <v>6771431</v>
+        <v>6771174</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13427,7 +13424,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13437,7 +13434,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13446,7 +13443,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13458,14 +13454,14 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125040000</v>
+        <v>125041900</v>
       </c>
       <c r="B118" t="n">
         <v>78947</v>
@@ -13499,19 +13495,22 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>380848</v>
+        <v>380872</v>
       </c>
       <c r="R118" t="n">
-        <v>6771174</v>
+        <v>6771195</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13540,7 +13539,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13550,7 +13549,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13559,25 +13558,26 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125041900</v>
+        <v>125070220</v>
       </c>
       <c r="B119" t="n">
         <v>78947</v>
@@ -13611,22 +13611,19 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>380872</v>
+        <v>381096</v>
       </c>
       <c r="R119" t="n">
-        <v>6771195</v>
+        <v>6771419</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13653,47 +13650,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>12:37</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125070220</v>
+        <v>125070261</v>
       </c>
       <c r="B120" t="n">
         <v>78947</v>
@@ -13733,10 +13719,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>381096</v>
+        <v>381036</v>
       </c>
       <c r="R120" t="n">
-        <v>6771419</v>
+        <v>6771447</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13795,10 +13781,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125070261</v>
+        <v>125070203</v>
       </c>
       <c r="B121" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13811,21 +13797,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13835,10 +13821,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>381036</v>
+        <v>381386</v>
       </c>
       <c r="R121" t="n">
-        <v>6771447</v>
+        <v>6771403</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13897,10 +13883,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125070203</v>
+        <v>125070218</v>
       </c>
       <c r="B122" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13913,21 +13899,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13937,10 +13923,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>381386</v>
+        <v>381266</v>
       </c>
       <c r="R122" t="n">
-        <v>6771403</v>
+        <v>6771351</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13999,7 +13985,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125070218</v>
+        <v>125070258</v>
       </c>
       <c r="B123" t="n">
         <v>78947</v>
@@ -14039,10 +14025,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>381266</v>
+        <v>380783</v>
       </c>
       <c r="R123" t="n">
-        <v>6771351</v>
+        <v>6771123</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -14101,10 +14087,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125070258</v>
+        <v>125050455</v>
       </c>
       <c r="B124" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14117,37 +14103,40 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>380783</v>
+        <v>381361</v>
       </c>
       <c r="R124" t="n">
-        <v>6771123</v>
+        <v>6770935</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14174,39 +14163,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125046088</v>
+        <v>125070210</v>
       </c>
       <c r="B125" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14219,40 +14219,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>381037</v>
+        <v>381370</v>
       </c>
       <c r="R125" t="n">
-        <v>6771430</v>
+        <v>6771255</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14279,47 +14276,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125044964</v>
+        <v>125070268</v>
       </c>
       <c r="B126" t="n">
         <v>78947</v>
@@ -14353,22 +14339,19 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>380889</v>
+        <v>380854</v>
       </c>
       <c r="R126" t="n">
-        <v>6771526</v>
+        <v>6771477</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -14395,47 +14378,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125045211</v>
+        <v>125070237</v>
       </c>
       <c r="B127" t="n">
         <v>78947</v>
@@ -14469,22 +14441,19 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>380887</v>
+        <v>380923</v>
       </c>
       <c r="R127" t="n">
-        <v>6771583</v>
+        <v>6771536</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14511,50 +14480,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125070199</v>
+        <v>125044964</v>
       </c>
       <c r="B128" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14567,37 +14525,40 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>380948</v>
+        <v>380889</v>
       </c>
       <c r="R128" t="n">
-        <v>6771512</v>
+        <v>6771526</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14624,36 +14585,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125070210</v>
+        <v>125045211</v>
       </c>
       <c r="B129" t="n">
         <v>78947</v>
@@ -14687,19 +14659,22 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>381370</v>
+        <v>380887</v>
       </c>
       <c r="R129" t="n">
-        <v>6771255</v>
+        <v>6771583</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14726,39 +14701,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125070268</v>
+        <v>125046088</v>
       </c>
       <c r="B130" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14771,37 +14757,40 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>380854</v>
+        <v>381037</v>
       </c>
       <c r="R130" t="n">
-        <v>6771477</v>
+        <v>6771430</v>
       </c>
       <c r="S130" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14828,39 +14817,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125070237</v>
+        <v>125070199</v>
       </c>
       <c r="B131" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14873,21 +14873,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14897,10 +14897,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>380923</v>
+        <v>380948</v>
       </c>
       <c r="R131" t="n">
-        <v>6771536</v>
+        <v>6771512</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -18432,7 +18432,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125045518</v>
+        <v>125070229</v>
       </c>
       <c r="B164" t="n">
         <v>78947</v>
@@ -18466,22 +18466,19 @@
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>380930</v>
+        <v>380971</v>
       </c>
       <c r="R164" t="n">
-        <v>6771540</v>
+        <v>6771489</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18508,50 +18505,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125045458</v>
+        <v>125045518</v>
       </c>
       <c r="B165" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18564,21 +18550,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18587,17 +18573,17 @@
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>380944</v>
+        <v>380930</v>
       </c>
       <c r="R165" t="n">
-        <v>6771491</v>
+        <v>6771540</v>
       </c>
       <c r="S165" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18626,7 +18612,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18636,7 +18622,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18652,19 +18638,19 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125049662</v>
+        <v>125045458</v>
       </c>
       <c r="B166" t="n">
         <v>78683</v>
@@ -18703,17 +18689,17 @@
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>381341</v>
+        <v>380944</v>
       </c>
       <c r="R166" t="n">
-        <v>6771287</v>
+        <v>6771491</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -18742,7 +18728,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18752,7 +18738,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18768,22 +18754,22 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125070229</v>
+        <v>125049662</v>
       </c>
       <c r="B167" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18796,37 +18782,40 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>380971</v>
+        <v>381341</v>
       </c>
       <c r="R167" t="n">
-        <v>6771489</v>
+        <v>6771287</v>
       </c>
       <c r="S167" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -18853,29 +18842,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -7463,10 +7463,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125047288</v>
+        <v>125070252</v>
       </c>
       <c r="B63" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7479,40 +7479,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>381041</v>
+        <v>380991</v>
       </c>
       <c r="R63" t="n">
-        <v>6771405</v>
+        <v>6771255</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7539,47 +7536,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:31</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125070269</v>
+        <v>125070235</v>
       </c>
       <c r="B64" t="n">
         <v>78947</v>
@@ -7619,10 +7605,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>380938</v>
+        <v>380941</v>
       </c>
       <c r="R64" t="n">
-        <v>6771234</v>
+        <v>6771522</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7681,7 +7667,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125044489</v>
+        <v>125070232</v>
       </c>
       <c r="B65" t="n">
         <v>78947</v>
@@ -7715,22 +7701,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>380835</v>
+        <v>380944</v>
       </c>
       <c r="R65" t="n">
-        <v>6771422</v>
+        <v>6771499</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7757,47 +7740,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125044246</v>
+        <v>125070248</v>
       </c>
       <c r="B66" t="n">
         <v>78947</v>
@@ -7831,19 +7803,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>380900</v>
+        <v>380858</v>
       </c>
       <c r="R66" t="n">
-        <v>6771401</v>
+        <v>6771400</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7873,47 +7842,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125070252</v>
+        <v>125070269</v>
       </c>
       <c r="B67" t="n">
         <v>78947</v>
@@ -7953,10 +7911,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>380991</v>
+        <v>380938</v>
       </c>
       <c r="R67" t="n">
-        <v>6771255</v>
+        <v>6771234</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8015,7 +7973,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125070235</v>
+        <v>125070254</v>
       </c>
       <c r="B68" t="n">
         <v>78947</v>
@@ -8055,10 +8013,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>380941</v>
+        <v>380901</v>
       </c>
       <c r="R68" t="n">
-        <v>6771522</v>
+        <v>6771241</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8117,7 +8075,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125070232</v>
+        <v>125044489</v>
       </c>
       <c r="B69" t="n">
         <v>78947</v>
@@ -8151,19 +8109,22 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>380944</v>
+        <v>380835</v>
       </c>
       <c r="R69" t="n">
-        <v>6771499</v>
+        <v>6771422</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8190,36 +8151,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125070248</v>
+        <v>125044246</v>
       </c>
       <c r="B70" t="n">
         <v>78947</v>
@@ -8253,16 +8225,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>380858</v>
+        <v>380900</v>
       </c>
       <c r="R70" t="n">
-        <v>6771400</v>
+        <v>6771401</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8292,39 +8267,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125070254</v>
+        <v>125047288</v>
       </c>
       <c r="B71" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8337,37 +8323,40 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>380901</v>
+        <v>381041</v>
       </c>
       <c r="R71" t="n">
-        <v>6771241</v>
+        <v>6771405</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8394,39 +8383,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125040971</v>
+        <v>125070264</v>
       </c>
       <c r="B72" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8439,37 +8439,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>380824</v>
+        <v>380899</v>
       </c>
       <c r="R72" t="n">
-        <v>6771235</v>
+        <v>6771529</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8496,19 +8496,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8523,22 +8513,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125046449</v>
+        <v>125070270</v>
       </c>
       <c r="B73" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8551,34 +8541,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>380860</v>
+        <v>380826</v>
       </c>
       <c r="R73" t="n">
-        <v>6771171</v>
+        <v>6771195</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8608,19 +8598,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:21</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8635,22 +8615,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125070200</v>
+        <v>125050619</v>
       </c>
       <c r="B74" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8663,34 +8643,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>380812</v>
+        <v>381293</v>
       </c>
       <c r="R74" t="n">
-        <v>6771391</v>
+        <v>6770938</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8720,39 +8703,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125049925</v>
+        <v>125070253</v>
       </c>
       <c r="B75" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8765,40 +8759,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>381316</v>
+        <v>380966</v>
       </c>
       <c r="R75" t="n">
-        <v>6771194</v>
+        <v>6771241</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8825,47 +8816,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125045722</v>
+        <v>125070250</v>
       </c>
       <c r="B76" t="n">
         <v>78947</v>
@@ -8899,22 +8879,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>380944</v>
+        <v>380990</v>
       </c>
       <c r="R76" t="n">
-        <v>6771491</v>
+        <v>6771182</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8941,50 +8918,39 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125070264</v>
+        <v>125070200</v>
       </c>
       <c r="B77" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8997,21 +8963,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9021,10 +8987,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>380899</v>
+        <v>380812</v>
       </c>
       <c r="R77" t="n">
-        <v>6771529</v>
+        <v>6771391</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -9083,10 +9049,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125070270</v>
+        <v>125049925</v>
       </c>
       <c r="B78" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9099,37 +9065,40 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>380826</v>
+        <v>381316</v>
       </c>
       <c r="R78" t="n">
-        <v>6771195</v>
+        <v>6771194</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9156,39 +9125,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125050619</v>
+        <v>125045722</v>
       </c>
       <c r="B79" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9201,21 +9181,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9224,17 +9204,17 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>381293</v>
+        <v>380944</v>
       </c>
       <c r="R79" t="n">
-        <v>6770938</v>
+        <v>6771491</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9263,7 +9243,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9273,7 +9253,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9289,22 +9269,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125070253</v>
+        <v>125040971</v>
       </c>
       <c r="B80" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9317,37 +9297,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>380966</v>
+        <v>380824</v>
       </c>
       <c r="R80" t="n">
-        <v>6771241</v>
+        <v>6771235</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9374,9 +9354,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9391,22 +9381,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125070250</v>
+        <v>125046449</v>
       </c>
       <c r="B81" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9419,34 +9409,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>380990</v>
+        <v>380860</v>
       </c>
       <c r="R81" t="n">
-        <v>6771182</v>
+        <v>6771171</v>
       </c>
       <c r="S81" t="n">
         <v>15</v>
@@ -9476,9 +9466,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9493,19 +9493,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson, Cecilia Rastad, Göran Ehn, Lisa Olson, Cecilia Rastad, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125039429</v>
+        <v>125070214</v>
       </c>
       <c r="B82" t="n">
         <v>78947</v>
@@ -9541,14 +9541,14 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>380933</v>
+        <v>381359</v>
       </c>
       <c r="R82" t="n">
-        <v>6771152</v>
+        <v>6771390</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9578,19 +9578,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9617,10 +9607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125040104</v>
+        <v>125070234</v>
       </c>
       <c r="B83" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9633,37 +9623,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>380842</v>
+        <v>380940</v>
       </c>
       <c r="R83" t="n">
-        <v>6771175</v>
+        <v>6771511</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9690,19 +9680,9 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9717,22 +9697,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125045567</v>
+        <v>125070205</v>
       </c>
       <c r="B84" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9745,40 +9725,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>380944</v>
+        <v>380806</v>
       </c>
       <c r="R84" t="n">
-        <v>6771491</v>
+        <v>6771391</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9805,47 +9782,36 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125044233</v>
+        <v>125045567</v>
       </c>
       <c r="B85" t="n">
         <v>78684</v>
@@ -9884,17 +9850,17 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>380900</v>
+        <v>380944</v>
       </c>
       <c r="R85" t="n">
-        <v>6771401</v>
+        <v>6771491</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9923,7 +9889,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9933,7 +9899,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9949,22 +9915,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125046257</v>
+        <v>125044233</v>
       </c>
       <c r="B86" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9977,21 +9943,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10000,17 +9966,17 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>381041</v>
+        <v>380900</v>
       </c>
       <c r="R86" t="n">
-        <v>6771405</v>
+        <v>6771401</v>
       </c>
       <c r="S86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10039,7 +10005,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10049,7 +10015,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10065,19 +10031,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125046145</v>
+        <v>125039429</v>
       </c>
       <c r="B87" t="n">
         <v>78947</v>
@@ -10111,19 +10077,16 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>381076</v>
+        <v>380933</v>
       </c>
       <c r="R87" t="n">
-        <v>6771400</v>
+        <v>6771152</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -10155,7 +10118,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10165,7 +10128,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10174,29 +10137,28 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125070214</v>
+        <v>125040104</v>
       </c>
       <c r="B88" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10209,37 +10171,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>381359</v>
+        <v>380842</v>
       </c>
       <c r="R88" t="n">
-        <v>6771390</v>
+        <v>6771175</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10266,9 +10228,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10283,19 +10255,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125070234</v>
+        <v>125046257</v>
       </c>
       <c r="B89" t="n">
         <v>78947</v>
@@ -10329,19 +10301,22 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abborrtjärnen, Abborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>380940</v>
+        <v>381041</v>
       </c>
       <c r="R89" t="n">
-        <v>6771511</v>
+        <v>6771405</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10368,39 +10343,50 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125070205</v>
+        <v>125046145</v>
       </c>
       <c r="B90" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10413,34 +10399,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>380806</v>
+        <v>381076</v>
       </c>
       <c r="R90" t="n">
-        <v>6771391</v>
+        <v>6771400</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -10470,29 +10459,40 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -13233,10 +13233,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125044507</v>
+        <v>125050455</v>
       </c>
       <c r="B116" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13249,21 +13249,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13276,10 +13276,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>380829</v>
+        <v>381361</v>
       </c>
       <c r="R116" t="n">
-        <v>6771431</v>
+        <v>6770935</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13311,7 +13311,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13342,14 +13342,14 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125040000</v>
+        <v>125044507</v>
       </c>
       <c r="B117" t="n">
         <v>78947</v>
@@ -13383,19 +13383,22 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Abelåsen, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>380848</v>
+        <v>380829</v>
       </c>
       <c r="R117" t="n">
-        <v>6771174</v>
+        <v>6771431</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13424,7 +13427,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13434,7 +13437,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13443,6 +13446,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13454,14 +13458,14 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125041900</v>
+        <v>125040000</v>
       </c>
       <c r="B118" t="n">
         <v>78947</v>
@@ -13495,22 +13499,19 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>380872</v>
+        <v>380848</v>
       </c>
       <c r="R118" t="n">
-        <v>6771195</v>
+        <v>6771174</v>
       </c>
       <c r="S118" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13539,7 +13540,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13549,7 +13550,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13558,26 +13559,25 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125070220</v>
+        <v>125041900</v>
       </c>
       <c r="B119" t="n">
         <v>78947</v>
@@ -13611,19 +13611,22 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>N. Lötsjön, Dlr</t>
+          <t>Abelåsen, Abelåsen, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>381096</v>
+        <v>380872</v>
       </c>
       <c r="R119" t="n">
-        <v>6771419</v>
+        <v>6771195</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13650,36 +13653,47 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson, Cecilia Rastad, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125070261</v>
+        <v>125070220</v>
       </c>
       <c r="B120" t="n">
         <v>78947</v>
@@ -13719,10 +13733,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>381036</v>
+        <v>381096</v>
       </c>
       <c r="R120" t="n">
-        <v>6771447</v>
+        <v>6771419</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13781,10 +13795,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125070203</v>
+        <v>125070261</v>
       </c>
       <c r="B121" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13797,21 +13811,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13821,10 +13835,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>381386</v>
+        <v>381036</v>
       </c>
       <c r="R121" t="n">
-        <v>6771403</v>
+        <v>6771447</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13883,10 +13897,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125070218</v>
+        <v>125070203</v>
       </c>
       <c r="B122" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13899,21 +13913,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13923,10 +13937,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>381266</v>
+        <v>381386</v>
       </c>
       <c r="R122" t="n">
-        <v>6771351</v>
+        <v>6771403</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13985,7 +13999,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125070258</v>
+        <v>125070218</v>
       </c>
       <c r="B123" t="n">
         <v>78947</v>
@@ -14025,10 +14039,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>380783</v>
+        <v>381266</v>
       </c>
       <c r="R123" t="n">
-        <v>6771123</v>
+        <v>6771351</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -14087,10 +14101,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125050455</v>
+        <v>125070258</v>
       </c>
       <c r="B124" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14103,40 +14117,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Abelåsen, Abelåsen, Dlr</t>
+          <t>N. Lötsjön, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>381361</v>
+        <v>380783</v>
       </c>
       <c r="R124" t="n">
-        <v>6770935</v>
+        <v>6771123</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -14163,40 +14174,29 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Lisa Olson, Göran Ehn</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -14634,7 +14634,7 @@
         <v>125070195</v>
       </c>
       <c r="B134" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 22112-2025 artfynd.xlsx
+++ b/artfynd/A 22112-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY194"/>
+  <dimension ref="A1:AZ194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328209</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328138</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125050754</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328168</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328139</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1287,6 +1317,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041283</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328120</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328127</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328177</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328192</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328146</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1869,6 +1929,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328207</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1976,6 +2041,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039429</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2083,6 +2153,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039570</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2190,6 +2265,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039628</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2297,6 +2377,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040000</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040046</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040078</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2618,6 +2713,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040285</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2725,6 +2825,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040302</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2832,6 +2937,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040775</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2939,6 +3049,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040890</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3046,6 +3161,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041099</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3153,6 +3273,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041252</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3260,6 +3385,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041650</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3367,6 +3497,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041757</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3478,6 +3613,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041900</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3589,6 +3729,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041954</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3700,6 +3845,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125042514</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3811,6 +3961,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125042305</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3922,6 +4077,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044246</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4033,6 +4193,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044277</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4149,6 +4314,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044410</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4260,6 +4430,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044477</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4371,6 +4546,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044481</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4482,6 +4662,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044489</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4593,6 +4778,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044547</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4704,6 +4894,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044507</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4815,6 +5010,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044513</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4926,6 +5126,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044939</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5037,6 +5242,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044979</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5148,6 +5358,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044995</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5259,6 +5474,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045155</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5370,6 +5590,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045211</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5481,6 +5706,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045234</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5592,6 +5822,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045250</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5703,6 +5938,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045265</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5814,6 +6054,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045320</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5925,6 +6170,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045722</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6036,6 +6286,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045518</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6147,6 +6402,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045538</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6258,6 +6518,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045848</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6369,6 +6634,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045953</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6480,6 +6750,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125046096</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6591,6 +6866,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125046145</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6702,6 +6982,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125046257</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6813,6 +7098,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125048909</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6924,6 +7214,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125048937</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7035,6 +7330,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125049404</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7146,6 +7446,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125049428</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7257,6 +7562,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125050078</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7354,6 +7664,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070207</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7451,6 +7766,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070208</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7548,6 +7868,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070209</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7645,6 +7970,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070210</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7742,6 +8072,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070211</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7839,6 +8174,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070212</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7936,6 +8276,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070213</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8033,6 +8378,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070214</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8130,6 +8480,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070215</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8227,6 +8582,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070216</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8324,6 +8684,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070217</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8421,6 +8786,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070218</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8518,6 +8888,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070219</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8615,6 +8990,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070220</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8712,6 +9092,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070221</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8809,6 +9194,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070222</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8906,6 +9296,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070224</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9003,6 +9398,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070227</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9100,6 +9500,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070228</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9197,6 +9602,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070229</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9294,6 +9704,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070230</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9391,6 +9806,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070231</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9488,6 +9908,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070232</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9585,6 +10010,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070233</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9682,6 +10112,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070234</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9779,6 +10214,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070235</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9876,6 +10316,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070236</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9973,6 +10418,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070237</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10070,6 +10520,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070238</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10167,6 +10622,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070239</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10264,6 +10724,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070240</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10361,6 +10826,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070241</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10458,6 +10928,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070242</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10555,6 +11030,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070243</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10652,6 +11132,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070244</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10749,6 +11234,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070245</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10846,6 +11336,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070247</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10943,6 +11438,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070248</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11040,6 +11540,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070249</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11137,6 +11642,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070250</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11234,6 +11744,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070251</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11331,6 +11846,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070252</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11428,6 +11948,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070253</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11525,6 +12050,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070254</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11622,6 +12152,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070255</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11719,6 +12254,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070256</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11816,6 +12356,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070258</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11913,6 +12458,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070259</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12010,6 +12560,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070260</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12107,6 +12662,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070261</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12204,6 +12764,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070263</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12301,6 +12866,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070264</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12398,6 +12968,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070265</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12495,6 +13070,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070266</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12592,6 +13172,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070267</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12689,6 +13274,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070268</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12786,6 +13376,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070269</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12883,6 +13478,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070270</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12980,6 +13580,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070271</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13082,6 +13687,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328212</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13179,6 +13789,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328159</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13276,6 +13891,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328187</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13383,6 +14003,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039727</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13490,6 +14115,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040104</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13601,6 +14231,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040199</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13708,6 +14343,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040971</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13815,6 +14455,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041868</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13922,6 +14567,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041901</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14033,6 +14683,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045458</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14144,6 +14799,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125046088</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14255,6 +14915,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125046579</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14366,6 +15031,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125048848</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14477,6 +15147,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125049508</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14588,6 +15263,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125049533</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14699,6 +15379,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125049662</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14810,6 +15495,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125049726</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14921,6 +15611,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125050284</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15032,6 +15727,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125050619</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15143,6 +15843,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125050680</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15240,6 +15945,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070202</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15337,6 +16047,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070203</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15434,6 +16149,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070204</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15531,6 +16251,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070205</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15628,6 +16353,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070206</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15725,6 +16455,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328118</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15822,6 +16557,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328158</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15933,6 +16673,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039976</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16040,6 +16785,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041141</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16151,6 +16901,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045357</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16262,6 +17017,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125046479</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16373,6 +17133,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125048940</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16470,6 +17235,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328149</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16581,6 +17351,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040931</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16683,6 +17458,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328126</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16785,6 +17565,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328147</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16887,6 +17672,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328211</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16997,6 +17787,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070195</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17112,6 +17907,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125046355</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17209,6 +18009,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328180</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17306,6 +18111,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328179</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17413,6 +18223,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039513</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17520,6 +18335,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125039568</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17631,6 +18451,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040653</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17738,6 +18563,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040326</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17845,6 +18675,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041208</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17956,6 +18791,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041905</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18067,6 +18907,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125042523</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18178,6 +19023,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044233</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18289,6 +19139,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044358</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18400,6 +19255,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044608</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18511,6 +19371,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125045567</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18622,6 +19487,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125046270</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18733,6 +19603,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125046556</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18844,6 +19719,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125047288</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18955,6 +19835,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125048854</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19066,6 +19951,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125049054</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19177,6 +20067,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125049925</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19288,6 +20183,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125050455</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19399,6 +20299,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125050542</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19496,6 +20401,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070199</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19593,6 +20503,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070200</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19690,6 +20605,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070201</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19787,6 +20707,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70328119</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19894,6 +20819,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040613</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20005,6 +20935,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125044862</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20102,6 +21037,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070190</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20199,6 +21139,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070191</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20296,6 +21241,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125070193</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20403,6 +21353,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040197</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20510,6 +21465,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040220</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20617,6 +21577,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125040739</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20728,8 +21693,208 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125049944</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>